--- a/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
@@ -1599,9 +1599,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}">
-  <dimension ref="A1:P475"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}">
+  <dimension ref="A1:H490"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="63" customWidth="1"/>
     <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -1611,7 +1611,7 @@
     <col min="8" max="8" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ns3:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ns3:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ns3:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ns3:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ns3:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ns3:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ns3:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ns3:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ns3:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ns3:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ns3:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>34</v>
       </c>
@@ -1785,7 +1785,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ns3:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>35</v>
       </c>
@@ -1812,7 +1812,7 @@
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ns3:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>36</v>
       </c>
@@ -1837,7 +1837,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ns3:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>277</v>
       </c>
@@ -1862,7 +1862,7 @@
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ns3:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>279</v>
       </c>
@@ -1887,7 +1887,7 @@
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ns3:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
@@ -1912,7 +1912,7 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ns3:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>281</v>
       </c>
@@ -1937,7 +1937,7 @@
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" ns3:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>282</v>
       </c>
@@ -1962,7 +1962,7 @@
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ns3:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>284</v>
       </c>
@@ -1987,7 +1987,7 @@
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" ns3:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>286</v>
       </c>
@@ -2011,7 +2011,7 @@
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ns3:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>276</v>
       </c>
@@ -2035,7 +2035,7 @@
       <c r="K24" s="4"/>
       <c r="O24" s="3"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" ns3:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>55</v>
       </c>
@@ -2061,7 +2061,7 @@
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" ns3:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>50</v>
       </c>
@@ -2087,7 +2087,7 @@
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ns3:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>288</v>
       </c>
@@ -2116,7 +2116,7 @@
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ns3:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>289</v>
       </c>
@@ -2145,7 +2145,7 @@
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ns3:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>291</v>
       </c>
@@ -2174,13 +2174,13 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ns3:dyDescent="0.2">
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ns3:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ns3:dyDescent="0.2">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ns3:dyDescent="0.2">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ns3:dyDescent="0.2">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" ns3:dyDescent="0.2">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ns3:dyDescent="0.2">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ns3:dyDescent="0.2">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ns3:dyDescent="0.2">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" ns3:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>12</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" ns3:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" ns3:dyDescent="0.2">
       <c r="A41" t="str">
         <f>B31</f>
         <v>polyacrylonitrile-based electrode production, for VRFB system</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I41" s="4"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ns3:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>292</v>
       </c>
@@ -2346,7 +2346,7 @@
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ns3:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>282</v>
       </c>
@@ -2373,7 +2373,7 @@
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ns3:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>282</v>
       </c>
@@ -2400,7 +2400,7 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" ns3:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>338</v>
       </c>
@@ -2427,7 +2427,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" ns3:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>50</v>
       </c>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="I46" s="4"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" ns3:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>65</v>
       </c>
@@ -2472,7 +2472,7 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" ns3:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>66</v>
       </c>
@@ -2497,13 +2497,13 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ns3:dyDescent="0.2">
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ns3:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>1</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ns3:dyDescent="0.2">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ns3:dyDescent="0.2">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" ns3:dyDescent="0.2">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" ns3:dyDescent="0.2">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ns3:dyDescent="0.2">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ns3:dyDescent="0.2">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" ns3:dyDescent="0.2">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" ns3:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>12</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" ns3:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>13</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" ns3:dyDescent="0.2">
       <c r="A60" t="str">
         <f>B50</f>
         <v>bipolar plate production, for VRFB system</v>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="I60" s="4"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" ns3:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>86</v>
       </c>
@@ -2669,7 +2669,7 @@
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" ns3:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>210</v>
       </c>
@@ -2696,7 +2696,7 @@
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" ns3:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>87</v>
       </c>
@@ -2723,7 +2723,7 @@
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" ns3:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>88</v>
       </c>
@@ -2750,7 +2750,7 @@
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" ns3:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>340</v>
       </c>
@@ -2777,7 +2777,7 @@
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" ns3:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>89</v>
       </c>
@@ -2804,7 +2804,7 @@
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" ns3:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>90</v>
       </c>
@@ -2831,7 +2831,7 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" ns3:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>322</v>
       </c>
@@ -2858,7 +2858,7 @@
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" ns3:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>342</v>
       </c>
@@ -2885,7 +2885,7 @@
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" ns3:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>91</v>
       </c>
@@ -2912,7 +2912,7 @@
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" ns3:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>282</v>
       </c>
@@ -2939,7 +2939,7 @@
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" ns3:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>282</v>
       </c>
@@ -2966,7 +2966,7 @@
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" ns3:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>358</v>
       </c>
@@ -2993,7 +2993,7 @@
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" ns3:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>344</v>
       </c>
@@ -3020,7 +3020,7 @@
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" ns3:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>286</v>
       </c>
@@ -3047,7 +3047,7 @@
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" ns3:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>289</v>
       </c>
@@ -3071,13 +3071,13 @@
       </c>
       <c r="I76" s="4"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" ns3:dyDescent="0.2">
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" ns3:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>1</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" ns3:dyDescent="0.2">
       <c r="A79" t="s">
         <v>3</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" ns3:dyDescent="0.2">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" ns3:dyDescent="0.2">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" ns3:dyDescent="0.2">
       <c r="A82" t="s">
         <v>7</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" ns3:dyDescent="0.2">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" ns3:dyDescent="0.2">
       <c r="A84" t="s">
         <v>9</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" ns3:dyDescent="0.2">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" ns3:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>12</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" ns3:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>13</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" ns3:dyDescent="0.2">
       <c r="A88" t="str">
         <f>B78</f>
         <v>stack frame assembly, for VRFB system</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="I88" s="4"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" ns3:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>109</v>
       </c>
@@ -3243,7 +3243,7 @@
       <c r="K89" s="3"/>
       <c r="L89" s="3"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" ns3:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>346</v>
       </c>
@@ -3270,7 +3270,7 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" ns3:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>110</v>
       </c>
@@ -3297,7 +3297,7 @@
       <c r="K91" s="3"/>
       <c r="L91" s="3"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" ns3:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>344</v>
       </c>
@@ -3324,7 +3324,7 @@
       <c r="K92" s="3"/>
       <c r="L92" s="3"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" ns3:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>286</v>
       </c>
@@ -3351,7 +3351,7 @@
       <c r="K93" s="3"/>
       <c r="L93" s="3"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" ns3:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>1</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" ns3:dyDescent="0.2">
       <c r="A96" t="s">
         <v>3</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" ns3:dyDescent="0.2">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -3384,15 +3384,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" ns3:dyDescent="0.2">
       <c r="A98" t="s">
         <v>6</v>
       </c>
-      <c r="B98" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ns3:dyDescent="0.2">
       <c r="A99" t="s">
         <v>7</v>
       </c>
@@ -3400,7 +3402,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" ns3:dyDescent="0.2">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -3411,7 +3413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" ns3:dyDescent="0.2">
       <c r="A101" t="s">
         <v>9</v>
       </c>
@@ -3422,7 +3424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" ns3:dyDescent="0.2">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -3433,7 +3435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" ns3:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>12</v>
       </c>
@@ -3441,7 +3443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" ns3:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>13</v>
       </c>
@@ -3467,7 +3469,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" ns3:dyDescent="0.2">
       <c r="A105" t="str">
         <f>B95</f>
         <v>vanadium electrolyte solution production</v>
@@ -3493,12 +3495,12 @@
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" ns3:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>122</v>
       </c>
       <c r="B106" s="3">
-        <v>0.28599999999999998</v>
+        <v>0.10698705882352941</v>
       </c>
       <c r="C106" t="s">
         <v>124</v>
@@ -3520,12 +3522,12 @@
       <c r="K106" s="3"/>
       <c r="L106" s="3"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" ns3:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>120</v>
       </c>
       <c r="B107" s="3">
-        <v>0.19600000000000001</v>
+        <v>0.3028910294117647</v>
       </c>
       <c r="C107" t="s">
         <v>4</v>
@@ -3547,12 +3549,12 @@
       <c r="K107" s="3"/>
       <c r="L107" s="3"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" ns3:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>348</v>
       </c>
       <c r="B108" s="6">
-        <v>4.8989999999999997E-3</v>
+        <v>0.0036027205882352936</v>
       </c>
       <c r="C108" t="s">
         <v>28</v>
@@ -3574,39 +3576,49 @@
       <c r="K108" s="3"/>
       <c r="L108" s="3"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A109" s="3" t="s">
-        <v>342</v>
+    <row r="109" spans="1:13" ns3:dyDescent="0.2">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>vanadium electrolyte conditioning, reference design</t>
+        </is>
       </c>
       <c r="B109" s="3">
-        <v>0.86299999999999999</v>
-      </c>
-      <c r="C109" t="s">
-        <v>29</v>
-      </c>
-      <c r="D109" t="s">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="F109" t="s">
         <v>30</v>
       </c>
-      <c r="G109" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>77</v>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>vanadium electrolyte conditioning, reference design</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>Conditioning service per kg final electrolyte: make-up water, V reduction electricity and O2 output. Materials remain separate.</t>
+        </is>
       </c>
       <c r="I109" s="3"/>
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
       <c r="L109" s="3"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" ns3:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>344</v>
       </c>
       <c r="B110" s="3">
-        <v>0.02</v>
+        <v>0.007481612505141917</v>
       </c>
       <c r="C110" t="s">
         <v>4</v>
@@ -3620,20 +3632,22 @@
       <c r="G110" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="H110" s="3" t="s">
-        <v>81</v>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>Historical S8 route-distance proxy, scaled with the corrected V2O5 shipment mass, per kg final solution.</t>
+        </is>
       </c>
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
       <c r="L110" s="3"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" ns3:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>286</v>
       </c>
       <c r="B111" s="3">
-        <v>0.121</v>
+        <v>0.045263755656108594</v>
       </c>
       <c r="C111" t="s">
         <v>29</v>
@@ -3647,20 +3661,22 @@
       <c r="G111" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="H111" s="3" t="s">
-        <v>82</v>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>Historical S8 route-distance proxy, scaled with the corrected V2O5 shipment mass, per kg final solution.</t>
+        </is>
       </c>
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
       <c r="L111" s="3"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" ns3:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>350</v>
       </c>
       <c r="B112" s="3">
-        <v>3.8130000000000002</v>
+        <v>1.4263694241053064</v>
       </c>
       <c r="C112" t="s">
         <v>28</v>
@@ -3674,20 +3690,22 @@
       <c r="G112" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="H112" s="3" t="s">
-        <v>117</v>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>Historical S8 route-distance proxy, scaled with the corrected V2O5 shipment mass, per kg final solution.</t>
+        </is>
       </c>
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
       <c r="L112" s="3"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" ns3:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>352</v>
       </c>
       <c r="B113" s="3">
-        <v>0.17299999999999999</v>
+        <v>0.06471594816947758</v>
       </c>
       <c r="C113" t="s">
         <v>4</v>
@@ -3701,20 +3719,22 @@
       <c r="G113" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="H113" s="3" t="s">
-        <v>118</v>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>Historical S8 route-distance proxy, scaled with the corrected V2O5 shipment mass, per kg final solution.</t>
+        </is>
       </c>
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
       <c r="K113" s="3"/>
       <c r="L113" s="3"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" ns3:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>284</v>
       </c>
       <c r="B114" s="3">
-        <v>0.187</v>
+        <v>0.06995307692307692</v>
       </c>
       <c r="C114" t="s">
         <v>4</v>
@@ -3728,11 +3748,13 @@
       <c r="G114" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="H114" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>Historical S8 route-distance proxy, scaled with the corrected V2O5 shipment mass, per kg final solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" spans="1:13" ns3:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>1</v>
       </c>
@@ -3743,7 +3765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" ns3:dyDescent="0.2">
       <c r="A117" t="s">
         <v>3</v>
       </c>
@@ -3754,7 +3776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" ns3:dyDescent="0.2">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -3765,7 +3787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" ns3:dyDescent="0.2">
       <c r="A119" t="s">
         <v>6</v>
       </c>
@@ -3773,7 +3795,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" ns3:dyDescent="0.2">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -3781,7 +3803,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" ns3:dyDescent="0.2">
       <c r="A121" t="s">
         <v>8</v>
       </c>
@@ -3792,7 +3814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" ns3:dyDescent="0.2">
       <c r="A122" t="s">
         <v>9</v>
       </c>
@@ -3803,7 +3825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" ns3:dyDescent="0.2">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -3814,7 +3836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" ns3:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>12</v>
       </c>
@@ -3822,7 +3844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" ns3:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>13</v>
       </c>
@@ -3848,7 +3870,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" ns3:dyDescent="0.2">
       <c r="A126" t="str">
         <f>B116</f>
         <v>electrolyte tank production, for VRFB system</v>
@@ -3874,7 +3896,7 @@
       <c r="K126" s="3"/>
       <c r="L126" s="3"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" ns3:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>130</v>
       </c>
@@ -3898,7 +3920,7 @@
       <c r="K127" s="3"/>
       <c r="L127" s="3"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" ns3:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>332</v>
       </c>
@@ -3922,7 +3944,7 @@
       <c r="K128" s="3"/>
       <c r="L128" s="3"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" ns3:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>131</v>
       </c>
@@ -3946,7 +3968,7 @@
       <c r="K129" s="3"/>
       <c r="L129" s="3"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" ns3:dyDescent="0.2">
       <c r="A130" s="3" t="s">
         <v>354</v>
       </c>
@@ -3970,7 +3992,7 @@
       <c r="K130" s="3"/>
       <c r="L130" s="3"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" ns3:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>158</v>
       </c>
@@ -3994,7 +4016,7 @@
       <c r="K131" s="3"/>
       <c r="L131" s="3"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" ns3:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>286</v>
       </c>
@@ -4021,7 +4043,7 @@
       <c r="K132" s="3"/>
       <c r="L132" s="3"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" ns3:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>344</v>
       </c>
@@ -4045,7 +4067,7 @@
       <c r="K133" s="3"/>
       <c r="L133" s="3"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" ns3:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>350</v>
       </c>
@@ -4069,7 +4091,7 @@
       <c r="K134" s="3"/>
       <c r="L134" s="3"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" ns3:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>336</v>
       </c>
@@ -4090,7 +4112,7 @@
       </c>
       <c r="I135" s="4"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" ns3:dyDescent="0.2">
       <c r="A136" s="3" t="s">
         <v>129</v>
       </c>
@@ -4111,13 +4133,13 @@
       <c r="K136" s="3"/>
       <c r="L136" s="3"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" ns3:dyDescent="0.2">
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="3"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" ns3:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>1</v>
       </c>
@@ -4128,7 +4150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" ns3:dyDescent="0.2">
       <c r="A139" t="s">
         <v>3</v>
       </c>
@@ -4139,7 +4161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" ns3:dyDescent="0.2">
       <c r="A140" t="s">
         <v>5</v>
       </c>
@@ -4150,7 +4172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" ns3:dyDescent="0.2">
       <c r="A141" t="s">
         <v>6</v>
       </c>
@@ -4158,7 +4180,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" ns3:dyDescent="0.2">
       <c r="A142" t="s">
         <v>7</v>
       </c>
@@ -4166,7 +4188,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" ns3:dyDescent="0.2">
       <c r="A143" t="s">
         <v>8</v>
       </c>
@@ -4177,7 +4199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13" ns3:dyDescent="0.2">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -4188,7 +4210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:13" ns3:dyDescent="0.2">
       <c r="A145" t="s">
         <v>11</v>
       </c>
@@ -4199,7 +4221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:13" ns3:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>12</v>
       </c>
@@ -4207,7 +4229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:13" ns3:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>13</v>
       </c>
@@ -4234,7 +4256,7 @@
       </c>
       <c r="I147" s="4"/>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13" ns3:dyDescent="0.2">
       <c r="A148" t="str">
         <f>B138</f>
         <v>current collector production, for VRFB system</v>
@@ -4260,7 +4282,7 @@
       <c r="K148" s="3"/>
       <c r="L148" s="3"/>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:13" ns3:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>324</v>
       </c>
@@ -4287,7 +4309,7 @@
       <c r="K149" s="3"/>
       <c r="L149" s="3"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:13" ns3:dyDescent="0.2">
       <c r="A150" s="3" t="s">
         <v>141</v>
       </c>
@@ -4314,7 +4336,7 @@
       <c r="K150" s="3"/>
       <c r="L150" s="3"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:13" ns3:dyDescent="0.2">
       <c r="A151" s="3" t="s">
         <v>356</v>
       </c>
@@ -4341,7 +4363,7 @@
       <c r="K151" s="3"/>
       <c r="L151" s="3"/>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:13" ns3:dyDescent="0.2">
       <c r="A152" s="3" t="s">
         <v>344</v>
       </c>
@@ -4368,7 +4390,7 @@
       <c r="K152" s="3"/>
       <c r="L152" s="3"/>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:13" ns3:dyDescent="0.2">
       <c r="A153" s="3" t="s">
         <v>286</v>
       </c>
@@ -4392,13 +4414,13 @@
       </c>
       <c r="I153" s="4"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:13" ns3:dyDescent="0.2">
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="3"/>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13" ns3:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>1</v>
       </c>
@@ -4409,7 +4431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:13" ns3:dyDescent="0.2">
       <c r="A156" t="s">
         <v>3</v>
       </c>
@@ -4420,7 +4442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13" ns3:dyDescent="0.2">
       <c r="A157" t="s">
         <v>5</v>
       </c>
@@ -4431,7 +4453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:13" ns3:dyDescent="0.2">
       <c r="A158" t="s">
         <v>6</v>
       </c>
@@ -4439,7 +4461,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:13" ns3:dyDescent="0.2">
       <c r="A159" t="s">
         <v>7</v>
       </c>
@@ -4447,7 +4469,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:13" ns3:dyDescent="0.2">
       <c r="A160" t="s">
         <v>8</v>
       </c>
@@ -4458,7 +4480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13" ns3:dyDescent="0.2">
       <c r="A161" t="s">
         <v>9</v>
       </c>
@@ -4469,7 +4491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:13" ns3:dyDescent="0.2">
       <c r="A162" t="s">
         <v>11</v>
       </c>
@@ -4480,7 +4502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:13" ns3:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>12</v>
       </c>
@@ -4488,7 +4510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13" ns3:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>13</v>
       </c>
@@ -4515,7 +4537,7 @@
       </c>
       <c r="I164" s="4"/>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:13" ns3:dyDescent="0.2">
       <c r="A165" t="str">
         <f>B155</f>
         <v>polyvinylchloride cell frame production, for VRFB system</v>
@@ -4538,7 +4560,7 @@
       </c>
       <c r="I165" s="4"/>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13" ns3:dyDescent="0.2">
       <c r="A166" s="3" t="s">
         <v>354</v>
       </c>
@@ -4563,7 +4585,7 @@
       <c r="K166" s="3"/>
       <c r="L166" s="3"/>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" ns3:dyDescent="0.2">
       <c r="A167" s="3" t="s">
         <v>158</v>
       </c>
@@ -4588,7 +4610,7 @@
       <c r="K167" s="3"/>
       <c r="L167" s="3"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13" ns3:dyDescent="0.2">
       <c r="A168" s="3" t="s">
         <v>286</v>
       </c>
@@ -4613,7 +4635,7 @@
       <c r="K168" s="3"/>
       <c r="L168" s="3"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:13" ns3:dyDescent="0.2">
       <c r="A169" s="3" t="s">
         <v>344</v>
       </c>
@@ -4638,7 +4660,7 @@
       <c r="K169" s="3"/>
       <c r="L169" s="3"/>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:13" ns3:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>1</v>
       </c>
@@ -4649,7 +4671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:13" ns3:dyDescent="0.2">
       <c r="A172" t="s">
         <v>3</v>
       </c>
@@ -4660,7 +4682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13" ns3:dyDescent="0.2">
       <c r="A173" t="s">
         <v>5</v>
       </c>
@@ -4671,7 +4693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:13" ns3:dyDescent="0.2">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -4679,7 +4701,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13" ns3:dyDescent="0.2">
       <c r="A175" t="s">
         <v>7</v>
       </c>
@@ -4687,7 +4709,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:13" ns3:dyDescent="0.2">
       <c r="A176" t="s">
         <v>8</v>
       </c>
@@ -4698,7 +4720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" ns3:dyDescent="0.2">
       <c r="A177" t="s">
         <v>9</v>
       </c>
@@ -4709,7 +4731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" ns3:dyDescent="0.2">
       <c r="A178" t="s">
         <v>11</v>
       </c>
@@ -4720,7 +4742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" ns3:dyDescent="0.2">
       <c r="A179" s="1" t="s">
         <v>12</v>
       </c>
@@ -4728,7 +4750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" ns3:dyDescent="0.2">
       <c r="A180" s="1" t="s">
         <v>13</v>
       </c>
@@ -4755,7 +4777,7 @@
       </c>
       <c r="I180" s="4"/>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" ns3:dyDescent="0.2">
       <c r="A181" t="str">
         <f>B171</f>
         <v>gasket production, FKM, for VRFB system</v>
@@ -4777,7 +4799,7 @@
         <v>gasket, FKM</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" ns3:dyDescent="0.2">
       <c r="A182" s="3" t="s">
         <v>156</v>
       </c>
@@ -4800,7 +4822,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" ns3:dyDescent="0.2">
       <c r="A183" s="3" t="s">
         <v>157</v>
       </c>
@@ -4823,7 +4845,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" ns3:dyDescent="0.2">
       <c r="A184" s="3" t="s">
         <v>334</v>
       </c>
@@ -4846,7 +4868,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" ns3:dyDescent="0.2">
       <c r="A185" s="3" t="s">
         <v>158</v>
       </c>
@@ -4869,7 +4891,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" ns3:dyDescent="0.2">
       <c r="A186" s="3" t="s">
         <v>286</v>
       </c>
@@ -4892,7 +4914,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" ns3:dyDescent="0.2">
       <c r="A187" s="3" t="s">
         <v>344</v>
       </c>
@@ -4915,7 +4937,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" ns3:dyDescent="0.2">
       <c r="A189" s="1" t="s">
         <v>1</v>
       </c>
@@ -4926,7 +4948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" ns3:dyDescent="0.2">
       <c r="A190" t="s">
         <v>3</v>
       </c>
@@ -4937,7 +4959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" ns3:dyDescent="0.2">
       <c r="A191" t="s">
         <v>5</v>
       </c>
@@ -4948,7 +4970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" ns3:dyDescent="0.2">
       <c r="A192" t="s">
         <v>6</v>
       </c>
@@ -4956,7 +4978,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:13" ns3:dyDescent="0.2">
       <c r="A193" t="s">
         <v>7</v>
       </c>
@@ -4964,7 +4986,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:13" ns3:dyDescent="0.2">
       <c r="A194" t="s">
         <v>8</v>
       </c>
@@ -4975,7 +4997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:13" ns3:dyDescent="0.2">
       <c r="A195" t="s">
         <v>9</v>
       </c>
@@ -4986,7 +5008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:13" ns3:dyDescent="0.2">
       <c r="A196" t="s">
         <v>11</v>
       </c>
@@ -4997,7 +5019,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:13" ns3:dyDescent="0.2">
       <c r="A197" s="1" t="s">
         <v>12</v>
       </c>
@@ -5005,7 +5027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:13" ns3:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>13</v>
       </c>
@@ -5032,7 +5054,7 @@
       </c>
       <c r="I198" s="4"/>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:13" ns3:dyDescent="0.2">
       <c r="A199" t="str">
         <f>B189</f>
         <v>copper cable production, for VRFB system</v>
@@ -5054,7 +5076,7 @@
         <v>copper cable, for VRFB system</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:13" ns3:dyDescent="0.2">
       <c r="A200" s="3" t="s">
         <v>167</v>
       </c>
@@ -5077,7 +5099,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:13" ns3:dyDescent="0.2">
       <c r="A201" s="3" t="s">
         <v>324</v>
       </c>
@@ -5100,7 +5122,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:13" ns3:dyDescent="0.2">
       <c r="A202" s="3" t="s">
         <v>354</v>
       </c>
@@ -5123,7 +5145,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" ns3:dyDescent="0.2">
       <c r="A203" s="3" t="s">
         <v>321</v>
       </c>
@@ -5146,7 +5168,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:13" ns3:dyDescent="0.2">
       <c r="A204" s="3" t="s">
         <v>158</v>
       </c>
@@ -5169,7 +5191,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:13" ns3:dyDescent="0.2">
       <c r="A205" s="3" t="s">
         <v>320</v>
       </c>
@@ -5192,7 +5214,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:13" ns3:dyDescent="0.2">
       <c r="A206" s="3" t="s">
         <v>344</v>
       </c>
@@ -5215,7 +5237,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:13" ns3:dyDescent="0.2">
       <c r="A207" s="3" t="s">
         <v>286</v>
       </c>
@@ -5238,7 +5260,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:13" ns3:dyDescent="0.2">
       <c r="A208" s="3" t="s">
         <v>330</v>
       </c>
@@ -5261,7 +5283,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:13" ns3:dyDescent="0.2">
       <c r="A209" s="3" t="s">
         <v>289</v>
       </c>
@@ -5284,7 +5306,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:13" ns3:dyDescent="0.2">
       <c r="A210" s="3" t="s">
         <v>77</v>
       </c>
@@ -5305,7 +5327,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:13" ns3:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>77</v>
       </c>
@@ -5325,7 +5347,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:13" ns3:dyDescent="0.2">
       <c r="A213" s="1" t="s">
         <v>1</v>
       </c>
@@ -5336,7 +5358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:13" ns3:dyDescent="0.2">
       <c r="A214" t="s">
         <v>3</v>
       </c>
@@ -5347,7 +5369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:13" ns3:dyDescent="0.2">
       <c r="A215" t="s">
         <v>5</v>
       </c>
@@ -5358,7 +5380,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:13" ns3:dyDescent="0.2">
       <c r="A216" t="s">
         <v>6</v>
       </c>
@@ -5366,7 +5388,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:13" ns3:dyDescent="0.2">
       <c r="A217" t="s">
         <v>7</v>
       </c>
@@ -5374,7 +5396,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:13" ns3:dyDescent="0.2">
       <c r="A218" t="s">
         <v>8</v>
       </c>
@@ -5385,7 +5407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:13" ns3:dyDescent="0.2">
       <c r="A219" t="s">
         <v>9</v>
       </c>
@@ -5396,7 +5418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:13" ns3:dyDescent="0.2">
       <c r="A220" t="s">
         <v>11</v>
       </c>
@@ -5407,7 +5429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:13" ns3:dyDescent="0.2">
       <c r="A221" s="1" t="s">
         <v>12</v>
       </c>
@@ -5415,7 +5437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:13" ns3:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>13</v>
       </c>
@@ -5442,7 +5464,7 @@
       </c>
       <c r="I222" s="4"/>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:13" ns3:dyDescent="0.2">
       <c r="A223" t="str">
         <f>B213</f>
         <v>pumps assembly, for VRFB system</v>
@@ -5468,7 +5490,7 @@
       <c r="K223" s="3"/>
       <c r="L223" s="3"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:13" ns3:dyDescent="0.2">
       <c r="A224" s="3" t="s">
         <v>328</v>
       </c>
@@ -5495,7 +5517,7 @@
       <c r="K224" s="3"/>
       <c r="L224" s="3"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:13" ns3:dyDescent="0.2">
       <c r="A225" s="3" t="s">
         <v>176</v>
       </c>
@@ -5522,7 +5544,7 @@
       <c r="K225" s="3"/>
       <c r="L225" s="3"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:13" ns3:dyDescent="0.2">
       <c r="A226" s="3" t="s">
         <v>324</v>
       </c>
@@ -5549,7 +5571,7 @@
       <c r="K226" s="3"/>
       <c r="L226" s="3"/>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:13" ns3:dyDescent="0.2">
       <c r="A227" s="3" t="s">
         <v>354</v>
       </c>
@@ -5576,7 +5598,7 @@
       <c r="K227" s="3"/>
       <c r="L227" s="3"/>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:13" ns3:dyDescent="0.2">
       <c r="A228" s="3" t="s">
         <v>326</v>
       </c>
@@ -5603,7 +5625,7 @@
       <c r="K228" s="3"/>
       <c r="L228" s="3"/>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:13" ns3:dyDescent="0.2">
       <c r="A229" s="3" t="s">
         <v>319</v>
       </c>
@@ -5630,7 +5652,7 @@
       <c r="K229" s="3"/>
       <c r="L229" s="3"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:13" ns3:dyDescent="0.2">
       <c r="A230" s="3" t="s">
         <v>318</v>
       </c>
@@ -5657,7 +5679,7 @@
       <c r="K230" s="3"/>
       <c r="L230" s="3"/>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:13" ns3:dyDescent="0.2">
       <c r="A231" s="3" t="s">
         <v>317</v>
       </c>
@@ -5684,7 +5706,7 @@
       <c r="K231" s="3"/>
       <c r="L231" s="3"/>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:13" ns3:dyDescent="0.2">
       <c r="A232" s="3" t="s">
         <v>344</v>
       </c>
@@ -5711,7 +5733,7 @@
       <c r="K232" s="3"/>
       <c r="L232" s="3"/>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:13" ns3:dyDescent="0.2">
       <c r="A233" s="3" t="s">
         <v>286</v>
       </c>
@@ -5735,7 +5757,7 @@
       </c>
       <c r="I233" s="4"/>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13" ns3:dyDescent="0.2">
       <c r="A234" s="3" t="s">
         <v>289</v>
       </c>
@@ -5762,7 +5784,7 @@
       <c r="K234" s="3"/>
       <c r="L234" s="3"/>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:13" ns3:dyDescent="0.2">
       <c r="A235" s="3" t="s">
         <v>311</v>
       </c>
@@ -5789,13 +5811,13 @@
       <c r="K235" s="3"/>
       <c r="L235" s="3"/>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13" ns3:dyDescent="0.2">
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
       <c r="L236" s="3"/>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:13" ns3:dyDescent="0.2">
       <c r="A237" s="1" t="s">
         <v>1</v>
       </c>
@@ -5806,7 +5828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13" ns3:dyDescent="0.2">
       <c r="A238" t="s">
         <v>3</v>
       </c>
@@ -5817,7 +5839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:13" ns3:dyDescent="0.2">
       <c r="A239" t="s">
         <v>5</v>
       </c>
@@ -5828,7 +5850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:13" ns3:dyDescent="0.2">
       <c r="A240" t="s">
         <v>6</v>
       </c>
@@ -5836,7 +5858,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13" ns3:dyDescent="0.2">
       <c r="A241" t="s">
         <v>7</v>
       </c>
@@ -5844,7 +5866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:13" ns3:dyDescent="0.2">
       <c r="A242" t="s">
         <v>8</v>
       </c>
@@ -5855,7 +5877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:13" ns3:dyDescent="0.2">
       <c r="A243" t="s">
         <v>9</v>
       </c>
@@ -5866,7 +5888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:13" ns3:dyDescent="0.2">
       <c r="A244" t="s">
         <v>11</v>
       </c>
@@ -5877,7 +5899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:13" ns3:dyDescent="0.2">
       <c r="A245" s="1" t="s">
         <v>12</v>
       </c>
@@ -5885,7 +5907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:13" ns3:dyDescent="0.2">
       <c r="A246" s="1" t="s">
         <v>13</v>
       </c>
@@ -5912,7 +5934,7 @@
       </c>
       <c r="I246" s="4"/>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:13" ns3:dyDescent="0.2">
       <c r="A247" t="str">
         <f>B237</f>
         <v>pipes assembly, for VRFB system</v>
@@ -5938,7 +5960,7 @@
       <c r="K247" s="3"/>
       <c r="L247" s="3"/>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:13" ns3:dyDescent="0.2">
       <c r="A248" s="3" t="s">
         <v>186</v>
       </c>
@@ -5965,7 +5987,7 @@
       <c r="K248" s="3"/>
       <c r="L248" s="3"/>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:13" ns3:dyDescent="0.2">
       <c r="A249" s="3" t="s">
         <v>309</v>
       </c>
@@ -5992,7 +6014,7 @@
       <c r="K249" s="3"/>
       <c r="L249" s="3"/>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:13" ns3:dyDescent="0.2">
       <c r="A250" s="3" t="s">
         <v>187</v>
       </c>
@@ -6019,7 +6041,7 @@
       <c r="K250" s="3"/>
       <c r="L250" s="3"/>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:13" ns3:dyDescent="0.2">
       <c r="A251" s="3" t="s">
         <v>344</v>
       </c>
@@ -6046,7 +6068,7 @@
       <c r="K251" s="3"/>
       <c r="L251" s="3"/>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:13" ns3:dyDescent="0.2">
       <c r="A252" s="3" t="s">
         <v>286</v>
       </c>
@@ -6070,13 +6092,13 @@
       </c>
       <c r="I252" s="4"/>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:13" ns3:dyDescent="0.2">
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
       <c r="L253" s="3"/>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:13" ns3:dyDescent="0.2">
       <c r="A254" s="1" t="s">
         <v>1</v>
       </c>
@@ -6087,7 +6109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:13" ns3:dyDescent="0.2">
       <c r="A255" t="s">
         <v>3</v>
       </c>
@@ -6098,7 +6120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:13" ns3:dyDescent="0.2">
       <c r="A256" t="s">
         <v>5</v>
       </c>
@@ -6109,7 +6131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:13" ns3:dyDescent="0.2">
       <c r="A257" t="s">
         <v>6</v>
       </c>
@@ -6117,7 +6139,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:13" ns3:dyDescent="0.2">
       <c r="A258" t="s">
         <v>7</v>
       </c>
@@ -6125,7 +6147,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:13" ns3:dyDescent="0.2">
       <c r="A259" t="s">
         <v>8</v>
       </c>
@@ -6136,7 +6158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13" ns3:dyDescent="0.2">
       <c r="A260" t="s">
         <v>9</v>
       </c>
@@ -6147,7 +6169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:13" ns3:dyDescent="0.2">
       <c r="A261" t="s">
         <v>11</v>
       </c>
@@ -6158,7 +6180,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:13" ns3:dyDescent="0.2">
       <c r="A262" s="1" t="s">
         <v>12</v>
       </c>
@@ -6166,7 +6188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:13" ns3:dyDescent="0.2">
       <c r="A263" s="1" t="s">
         <v>13</v>
       </c>
@@ -6193,7 +6215,7 @@
       </c>
       <c r="I263" s="4"/>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:13" ns3:dyDescent="0.2">
       <c r="A264" t="str">
         <f>B254</f>
         <v>heat exchanger production, for VRFB system</v>
@@ -6219,7 +6241,7 @@
       <c r="K264" s="3"/>
       <c r="L264" s="3"/>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:13" ns3:dyDescent="0.2">
       <c r="A265" s="3" t="s">
         <v>359</v>
       </c>
@@ -6242,7 +6264,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:13" ns3:dyDescent="0.2">
       <c r="A266" s="3" t="s">
         <v>193</v>
       </c>
@@ -6265,7 +6287,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:13" ns3:dyDescent="0.2">
       <c r="A267" s="3" t="s">
         <v>358</v>
       </c>
@@ -6289,7 +6311,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:13" ns3:dyDescent="0.2">
       <c r="A268" s="3" t="s">
         <v>282</v>
       </c>
@@ -6312,7 +6334,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:13" ns3:dyDescent="0.2">
       <c r="A269" s="3" t="s">
         <v>344</v>
       </c>
@@ -6335,7 +6357,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:13" ns3:dyDescent="0.2">
       <c r="A270" s="3" t="s">
         <v>286</v>
       </c>
@@ -6358,7 +6380,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:13" ns3:dyDescent="0.2">
       <c r="A272" s="1" t="s">
         <v>1</v>
       </c>
@@ -6369,7 +6391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:13" ns3:dyDescent="0.2">
       <c r="A273" t="s">
         <v>3</v>
       </c>
@@ -6380,7 +6402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:13" ns3:dyDescent="0.2">
       <c r="A274" t="s">
         <v>5</v>
       </c>
@@ -6391,7 +6413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:13" ns3:dyDescent="0.2">
       <c r="A275" t="s">
         <v>6</v>
       </c>
@@ -6399,7 +6421,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:13" ns3:dyDescent="0.2">
       <c r="A276" t="s">
         <v>7</v>
       </c>
@@ -6407,7 +6429,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:13" ns3:dyDescent="0.2">
       <c r="A277" t="s">
         <v>8</v>
       </c>
@@ -6418,7 +6440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:13" ns3:dyDescent="0.2">
       <c r="A278" t="s">
         <v>9</v>
       </c>
@@ -6429,7 +6451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:13" ns3:dyDescent="0.2">
       <c r="A279" t="s">
         <v>11</v>
       </c>
@@ -6440,7 +6462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:13" ns3:dyDescent="0.2">
       <c r="A280" s="1" t="s">
         <v>12</v>
       </c>
@@ -6448,7 +6470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:13" ns3:dyDescent="0.2">
       <c r="A281" s="1" t="s">
         <v>13</v>
       </c>
@@ -6475,7 +6497,7 @@
       </c>
       <c r="I281" s="4"/>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:13" ns3:dyDescent="0.2">
       <c r="A282" t="str">
         <f>B272</f>
         <v>stack monitoring interface assembly, for VRFB system</v>
@@ -6501,7 +6523,7 @@
       <c r="K282" s="3"/>
       <c r="L282" s="3"/>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:13" ns3:dyDescent="0.2">
       <c r="A283" s="3" t="s">
         <v>109</v>
       </c>
@@ -6524,7 +6546,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:13" ns3:dyDescent="0.2">
       <c r="A284" s="3" t="s">
         <v>206</v>
       </c>
@@ -6547,7 +6569,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:13" ns3:dyDescent="0.2">
       <c r="A285" s="3" t="s">
         <v>207</v>
       </c>
@@ -6570,7 +6592,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:13" ns3:dyDescent="0.2">
       <c r="A286" s="3" t="s">
         <v>208</v>
       </c>
@@ -6593,7 +6615,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:13" ns3:dyDescent="0.2">
       <c r="A287" s="3" t="s">
         <v>210</v>
       </c>
@@ -6616,7 +6638,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:13" ns3:dyDescent="0.2">
       <c r="A288" s="3" t="s">
         <v>209</v>
       </c>
@@ -6639,7 +6661,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13" ns3:dyDescent="0.2">
       <c r="A289" s="3" t="s">
         <v>294</v>
       </c>
@@ -6662,7 +6684,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:13" ns3:dyDescent="0.2">
       <c r="A290" s="3" t="s">
         <v>344</v>
       </c>
@@ -6685,7 +6707,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13" ns3:dyDescent="0.2">
       <c r="A291" s="3" t="s">
         <v>286</v>
       </c>
@@ -6708,10 +6730,10 @@
         <v>82</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13" ns3:dyDescent="0.2">
       <c r="H292" s="4"/>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13" ns3:dyDescent="0.2">
       <c r="A293" s="1" t="s">
         <v>1</v>
       </c>
@@ -6722,7 +6744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13" ns3:dyDescent="0.2">
       <c r="A294" t="s">
         <v>3</v>
       </c>
@@ -6733,7 +6755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13" ns3:dyDescent="0.2">
       <c r="A295" t="s">
         <v>5</v>
       </c>
@@ -6744,7 +6766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" ns3:dyDescent="0.2">
       <c r="A296" t="s">
         <v>6</v>
       </c>
@@ -6752,7 +6774,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13" ns3:dyDescent="0.2">
       <c r="A297" t="s">
         <v>7</v>
       </c>
@@ -6760,7 +6782,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" ns3:dyDescent="0.2">
       <c r="A298" t="s">
         <v>8</v>
       </c>
@@ -6771,7 +6793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13" ns3:dyDescent="0.2">
       <c r="A299" t="s">
         <v>9</v>
       </c>
@@ -6782,7 +6804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:13" ns3:dyDescent="0.2">
       <c r="A300" t="s">
         <v>11</v>
       </c>
@@ -6793,7 +6815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" ns3:dyDescent="0.2">
       <c r="A301" s="1" t="s">
         <v>12</v>
       </c>
@@ -6801,7 +6823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13" ns3:dyDescent="0.2">
       <c r="A302" s="1" t="s">
         <v>13</v>
       </c>
@@ -6828,7 +6850,7 @@
       </c>
       <c r="I302" s="4"/>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:13" ns3:dyDescent="0.2">
       <c r="A303" t="str">
         <f>B293</f>
         <v>battery management system assembly, for VRFB system</v>
@@ -6854,7 +6876,7 @@
       <c r="K303" s="3"/>
       <c r="L303" s="3"/>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:13" ns3:dyDescent="0.2">
       <c r="A304" s="3" t="s">
         <v>210</v>
       </c>
@@ -6877,7 +6899,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:13" ns3:dyDescent="0.2">
       <c r="A305" s="3" t="s">
         <v>294</v>
       </c>
@@ -6900,7 +6922,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:13" ns3:dyDescent="0.2">
       <c r="A306" s="3" t="s">
         <v>222</v>
       </c>
@@ -6923,7 +6945,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:13" ns3:dyDescent="0.2">
       <c r="A307" s="3" t="s">
         <v>223</v>
       </c>
@@ -6946,7 +6968,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:13" ns3:dyDescent="0.2">
       <c r="A308" s="3" t="s">
         <v>344</v>
       </c>
@@ -6969,7 +6991,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:13" ns3:dyDescent="0.2">
       <c r="A309" s="3" t="s">
         <v>286</v>
       </c>
@@ -6992,7 +7014,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:13" ns3:dyDescent="0.2">
       <c r="A311" s="1" t="s">
         <v>1</v>
       </c>
@@ -7003,7 +7025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:13" ns3:dyDescent="0.2">
       <c r="A312" t="s">
         <v>3</v>
       </c>
@@ -7014,7 +7036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:13" ns3:dyDescent="0.2">
       <c r="A313" t="s">
         <v>5</v>
       </c>
@@ -7025,7 +7047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:13" ns3:dyDescent="0.2">
       <c r="A314" t="s">
         <v>6</v>
       </c>
@@ -7033,7 +7055,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:13" ns3:dyDescent="0.2">
       <c r="A315" t="s">
         <v>7</v>
       </c>
@@ -7041,7 +7063,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:13" ns3:dyDescent="0.2">
       <c r="A316" t="s">
         <v>8</v>
       </c>
@@ -7052,7 +7074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:13" ns3:dyDescent="0.2">
       <c r="A317" t="s">
         <v>9</v>
       </c>
@@ -7063,7 +7085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:13" ns3:dyDescent="0.2">
       <c r="A318" t="s">
         <v>11</v>
       </c>
@@ -7074,7 +7096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:13" ns3:dyDescent="0.2">
       <c r="A319" s="1" t="s">
         <v>12</v>
       </c>
@@ -7082,7 +7104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:13" ns3:dyDescent="0.2">
       <c r="A320" s="1" t="s">
         <v>13</v>
       </c>
@@ -7109,7 +7131,7 @@
       </c>
       <c r="I320" s="4"/>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:13" ns3:dyDescent="0.2">
       <c r="A321" t="str">
         <f>B311</f>
         <v>process control system assembly, for VRFB system</v>
@@ -7135,7 +7157,7 @@
       <c r="K321" s="3"/>
       <c r="L321" s="3"/>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:13" ns3:dyDescent="0.2">
       <c r="A322" t="s">
         <v>196</v>
       </c>
@@ -7159,7 +7181,7 @@
       </c>
       <c r="L322" s="3"/>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:13" ns3:dyDescent="0.2">
       <c r="A323" t="s">
         <v>216</v>
       </c>
@@ -7183,7 +7205,7 @@
       </c>
       <c r="L323" s="3"/>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:13" ns3:dyDescent="0.2">
       <c r="A325" s="1" t="s">
         <v>1</v>
       </c>
@@ -7194,7 +7216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:13" ns3:dyDescent="0.2">
       <c r="A326" t="s">
         <v>3</v>
       </c>
@@ -7205,7 +7227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:13" ns3:dyDescent="0.2">
       <c r="A327" t="s">
         <v>5</v>
       </c>
@@ -7216,7 +7238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:13" ns3:dyDescent="0.2">
       <c r="A328" t="s">
         <v>7</v>
       </c>
@@ -7224,7 +7246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:13" ns3:dyDescent="0.2">
       <c r="A329" t="s">
         <v>8</v>
       </c>
@@ -7235,7 +7257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:13" ns3:dyDescent="0.2">
       <c r="A330" t="s">
         <v>9</v>
       </c>
@@ -7246,7 +7268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:13" ns3:dyDescent="0.2">
       <c r="A331" t="s">
         <v>11</v>
       </c>
@@ -7257,7 +7279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:13" ns3:dyDescent="0.2">
       <c r="A332" s="1" t="s">
         <v>12</v>
       </c>
@@ -7265,7 +7287,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:13" ns3:dyDescent="0.2">
       <c r="A333" s="1" t="s">
         <v>13</v>
       </c>
@@ -7292,7 +7314,7 @@
       </c>
       <c r="I333" s="4"/>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:13" ns3:dyDescent="0.2">
       <c r="A334" t="str">
         <f>B325</f>
         <v>treatment of stack, for VRFB system</v>
@@ -7318,7 +7340,7 @@
       <c r="K334" s="3"/>
       <c r="L334" s="3"/>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:13" ns3:dyDescent="0.2">
       <c r="A335" t="s">
         <v>307</v>
       </c>
@@ -7338,7 +7360,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:13" ns3:dyDescent="0.2">
       <c r="A336" t="s">
         <v>306</v>
       </c>
@@ -7358,7 +7380,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:13" ns3:dyDescent="0.2">
       <c r="A337" t="s">
         <v>304</v>
       </c>
@@ -7378,7 +7400,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:13" ns3:dyDescent="0.2">
       <c r="A338" t="s">
         <v>302</v>
       </c>
@@ -7398,7 +7420,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:13" ns3:dyDescent="0.2">
       <c r="A339" t="s">
         <v>301</v>
       </c>
@@ -7418,7 +7440,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:13" ns3:dyDescent="0.2">
       <c r="A340" t="s">
         <v>232</v>
       </c>
@@ -7438,7 +7460,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13" ns3:dyDescent="0.2">
       <c r="A341" t="s">
         <v>234</v>
       </c>
@@ -7458,7 +7480,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:13" ns3:dyDescent="0.2">
       <c r="A343" s="1" t="s">
         <v>1</v>
       </c>
@@ -7469,7 +7491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:13" ns3:dyDescent="0.2">
       <c r="A344" t="s">
         <v>3</v>
       </c>
@@ -7480,7 +7502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:13" ns3:dyDescent="0.2">
       <c r="A345" t="s">
         <v>5</v>
       </c>
@@ -7491,7 +7513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:13" ns3:dyDescent="0.2">
       <c r="A346" t="s">
         <v>7</v>
       </c>
@@ -7499,7 +7521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:13" ns3:dyDescent="0.2">
       <c r="A347" t="s">
         <v>8</v>
       </c>
@@ -7510,7 +7532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:13" ns3:dyDescent="0.2">
       <c r="A348" t="s">
         <v>9</v>
       </c>
@@ -7521,7 +7543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13" ns3:dyDescent="0.2">
       <c r="A349" t="s">
         <v>11</v>
       </c>
@@ -7532,7 +7554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13" ns3:dyDescent="0.2">
       <c r="A350" s="1" t="s">
         <v>12</v>
       </c>
@@ -7540,7 +7562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13" ns3:dyDescent="0.2">
       <c r="A351" s="1" t="s">
         <v>13</v>
       </c>
@@ -7567,7 +7589,7 @@
       </c>
       <c r="I351" s="4"/>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13" ns3:dyDescent="0.2">
       <c r="A352" t="str">
         <f>B343</f>
         <v>treatment of electrolyte tank, for VRFB system</v>
@@ -7593,7 +7615,7 @@
       <c r="K352" s="3"/>
       <c r="L352" s="3"/>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13" ns3:dyDescent="0.2">
       <c r="A353" t="s">
         <v>232</v>
       </c>
@@ -7613,7 +7635,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13" ns3:dyDescent="0.2">
       <c r="A354" s="3" t="s">
         <v>344</v>
       </c>
@@ -7636,7 +7658,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:13" ns3:dyDescent="0.2">
       <c r="A355" t="s">
         <v>306</v>
       </c>
@@ -7656,7 +7678,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:13" ns3:dyDescent="0.2">
       <c r="A357" s="1" t="s">
         <v>1</v>
       </c>
@@ -7667,7 +7689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:13" ns3:dyDescent="0.2">
       <c r="A358" t="s">
         <v>3</v>
       </c>
@@ -7678,7 +7700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:13" ns3:dyDescent="0.2">
       <c r="A359" t="s">
         <v>5</v>
       </c>
@@ -7689,7 +7711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:13" ns3:dyDescent="0.2">
       <c r="A360" t="s">
         <v>7</v>
       </c>
@@ -7697,7 +7719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:13" ns3:dyDescent="0.2">
       <c r="A361" t="s">
         <v>8</v>
       </c>
@@ -7708,7 +7730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:13" ns3:dyDescent="0.2">
       <c r="A362" t="s">
         <v>9</v>
       </c>
@@ -7719,7 +7741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:13" ns3:dyDescent="0.2">
       <c r="A363" t="s">
         <v>11</v>
       </c>
@@ -7730,7 +7752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:13" ns3:dyDescent="0.2">
       <c r="A364" s="1" t="s">
         <v>12</v>
       </c>
@@ -7738,7 +7760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:13" ns3:dyDescent="0.2">
       <c r="A365" s="1" t="s">
         <v>13</v>
       </c>
@@ -7765,7 +7787,7 @@
       </c>
       <c r="I365" s="4"/>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:13" ns3:dyDescent="0.2">
       <c r="A366" t="str">
         <f>B357</f>
         <v>treatment of electrolyte solution, for VRFB system</v>
@@ -7791,7 +7813,7 @@
       <c r="K366" s="3"/>
       <c r="L366" s="3"/>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:13" ns3:dyDescent="0.2">
       <c r="A367" t="s">
         <v>232</v>
       </c>
@@ -7811,7 +7833,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:13" ns3:dyDescent="0.2">
       <c r="A368" s="3" t="s">
         <v>344</v>
       </c>
@@ -7834,7 +7856,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:14" ns3:dyDescent="0.2">
       <c r="A370" s="1" t="s">
         <v>1</v>
       </c>
@@ -7845,7 +7867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:14" ns3:dyDescent="0.2">
       <c r="A371" t="s">
         <v>3</v>
       </c>
@@ -7856,7 +7878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:14" ns3:dyDescent="0.2">
       <c r="A372" t="s">
         <v>5</v>
       </c>
@@ -7867,7 +7889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:14" ns3:dyDescent="0.2">
       <c r="A373" t="s">
         <v>7</v>
       </c>
@@ -7875,7 +7897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:14" ns3:dyDescent="0.2">
       <c r="A374" t="s">
         <v>8</v>
       </c>
@@ -7886,7 +7908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:14" ns3:dyDescent="0.2">
       <c r="A375" t="s">
         <v>9</v>
       </c>
@@ -7897,7 +7919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:14" ns3:dyDescent="0.2">
       <c r="A376" t="s">
         <v>11</v>
       </c>
@@ -7908,7 +7930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:14" ns3:dyDescent="0.2">
       <c r="A377" s="1" t="s">
         <v>12</v>
       </c>
@@ -7916,7 +7938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:14" ns3:dyDescent="0.2">
       <c r="A378" s="1" t="s">
         <v>13</v>
       </c>
@@ -7943,7 +7965,7 @@
       </c>
       <c r="I378" s="4"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:14" ns3:dyDescent="0.2">
       <c r="A379" t="str">
         <f>B370</f>
         <v>treatment of periphericals, for VRFB system</v>
@@ -7971,7 +7993,7 @@
       <c r="M379" s="3"/>
       <c r="N379" s="3"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:14" ns3:dyDescent="0.2">
       <c r="A380" t="s">
         <v>232</v>
       </c>
@@ -7995,7 +8017,7 @@
       <c r="M380" s="3"/>
       <c r="N380" s="3"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:14" ns3:dyDescent="0.2">
       <c r="A381" t="s">
         <v>234</v>
       </c>
@@ -8019,7 +8041,7 @@
       <c r="M381" s="3"/>
       <c r="N381" s="3"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:14" ns3:dyDescent="0.2">
       <c r="A382" t="s">
         <v>302</v>
       </c>
@@ -8040,7 +8062,7 @@
       </c>
       <c r="K382" s="4"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:14" ns3:dyDescent="0.2">
       <c r="A383" t="s">
         <v>243</v>
       </c>
@@ -8064,7 +8086,7 @@
       <c r="M383" s="3"/>
       <c r="N383" s="3"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:14" ns3:dyDescent="0.2">
       <c r="A384" t="s">
         <v>245</v>
       </c>
@@ -8088,7 +8110,7 @@
       <c r="M384" s="3"/>
       <c r="N384" s="3"/>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:16" ns3:dyDescent="0.2">
       <c r="A385" t="s">
         <v>306</v>
       </c>
@@ -8112,13 +8134,13 @@
       <c r="M385" s="3"/>
       <c r="N385" s="3"/>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:16" ns3:dyDescent="0.2">
       <c r="K386" s="3"/>
       <c r="L386" s="3"/>
       <c r="M386" s="3"/>
       <c r="N386" s="3"/>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:16" ns3:dyDescent="0.2">
       <c r="A387" s="1" t="s">
         <v>1</v>
       </c>
@@ -8129,7 +8151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:16" ns3:dyDescent="0.2">
       <c r="A388" t="s">
         <v>3</v>
       </c>
@@ -8140,7 +8162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:16" ns3:dyDescent="0.2">
       <c r="A389" t="s">
         <v>6</v>
       </c>
@@ -8148,7 +8170,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:16" ns3:dyDescent="0.2">
       <c r="A390" t="s">
         <v>5</v>
       </c>
@@ -8159,7 +8181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:16" ns3:dyDescent="0.2">
       <c r="A391" t="s">
         <v>7</v>
       </c>
@@ -8167,7 +8189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:16" ns3:dyDescent="0.2">
       <c r="A392" t="s">
         <v>8</v>
       </c>
@@ -8178,7 +8200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:16" ns3:dyDescent="0.2">
       <c r="A393" t="s">
         <v>9</v>
       </c>
@@ -8189,7 +8211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:16" ns3:dyDescent="0.2">
       <c r="A394" t="s">
         <v>11</v>
       </c>
@@ -8200,7 +8222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:16" ns3:dyDescent="0.2">
       <c r="A395" s="1" t="s">
         <v>12</v>
       </c>
@@ -8208,7 +8230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:16" ns3:dyDescent="0.2">
       <c r="A396" s="1" t="s">
         <v>13</v>
       </c>
@@ -8235,7 +8257,7 @@
       </c>
       <c r="I396" s="4"/>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:16" ns3:dyDescent="0.2">
       <c r="A397" t="str">
         <f>B387</f>
         <v>vanadium-redox flow battery stack assembly</v>
@@ -8264,7 +8286,7 @@
       <c r="M397" s="3"/>
       <c r="N397" s="3"/>
     </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:16" ns3:dyDescent="0.2">
       <c r="A398" t="s">
         <v>18</v>
       </c>
@@ -8295,7 +8317,7 @@
       <c r="O398" s="2"/>
       <c r="P398" s="2"/>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:16" ns3:dyDescent="0.2">
       <c r="A399" t="s">
         <v>67</v>
       </c>
@@ -8324,7 +8346,7 @@
       <c r="N399" s="3"/>
       <c r="O399" s="3"/>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:16" ns3:dyDescent="0.2">
       <c r="A400" t="s">
         <v>363</v>
       </c>
@@ -8353,7 +8375,7 @@
       <c r="N400" s="3"/>
       <c r="O400" s="3"/>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:15" ns3:dyDescent="0.2">
       <c r="A401" t="s">
         <v>135</v>
       </c>
@@ -8382,7 +8404,7 @@
       <c r="N401" s="3"/>
       <c r="O401" s="3"/>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:15" ns3:dyDescent="0.2">
       <c r="A402" t="s">
         <v>143</v>
       </c>
@@ -8411,7 +8433,7 @@
       <c r="N402" s="3"/>
       <c r="O402" s="3"/>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:15" ns3:dyDescent="0.2">
       <c r="A403" t="s">
         <v>148</v>
       </c>
@@ -8440,7 +8462,7 @@
       <c r="N403" s="3"/>
       <c r="O403" s="3"/>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:15" ns3:dyDescent="0.2">
       <c r="A404" t="s">
         <v>100</v>
       </c>
@@ -8469,7 +8491,7 @@
       <c r="N404" s="3"/>
       <c r="O404" s="3"/>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:15" ns3:dyDescent="0.2">
       <c r="B405" s="3"/>
       <c r="H405" s="3"/>
       <c r="I405" s="3"/>
@@ -8479,7 +8501,7 @@
       <c r="N405" s="3"/>
       <c r="O405" s="3"/>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:15" ns3:dyDescent="0.2">
       <c r="A406" s="1" t="s">
         <v>1</v>
       </c>
@@ -8490,7 +8512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:15" ns3:dyDescent="0.2">
       <c r="A407" t="s">
         <v>3</v>
       </c>
@@ -8501,15 +8523,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:15" ns3:dyDescent="0.2">
       <c r="A408" t="s">
         <v>6</v>
       </c>
-      <c r="B408" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" spans="1:15" ns3:dyDescent="0.2">
       <c r="A409" t="s">
         <v>5</v>
       </c>
@@ -8520,7 +8544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:15" ns3:dyDescent="0.2">
       <c r="A410" t="s">
         <v>7</v>
       </c>
@@ -8528,7 +8552,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:15" ns3:dyDescent="0.2">
       <c r="A411" t="s">
         <v>8</v>
       </c>
@@ -8539,7 +8563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:15" ns3:dyDescent="0.2">
       <c r="A412" t="s">
         <v>9</v>
       </c>
@@ -8550,7 +8574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:15" ns3:dyDescent="0.2">
       <c r="A413" t="s">
         <v>11</v>
       </c>
@@ -8561,7 +8585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:15" ns3:dyDescent="0.2">
       <c r="A414" s="1" t="s">
         <v>12</v>
       </c>
@@ -8569,7 +8593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:15" ns3:dyDescent="0.2">
       <c r="A415" s="1" t="s">
         <v>13</v>
       </c>
@@ -8596,7 +8620,7 @@
       </c>
       <c r="I415" s="4"/>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:15" ns3:dyDescent="0.2">
       <c r="A416" t="str">
         <f>B406</f>
         <v>vanadium-redox flow battery system assembly, 8.3 megawatt hour</v>
@@ -8625,7 +8649,7 @@
       <c r="M416" s="3"/>
       <c r="N416" s="3"/>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:16" ns3:dyDescent="0.2">
       <c r="A417" t="s">
         <v>265</v>
       </c>
@@ -8656,7 +8680,7 @@
       <c r="O417" s="2"/>
       <c r="P417" s="2"/>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:16" ns3:dyDescent="0.2">
       <c r="A418" t="s">
         <v>112</v>
       </c>
@@ -8685,7 +8709,7 @@
       <c r="N418" s="3"/>
       <c r="O418" s="3"/>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:16" ns3:dyDescent="0.2">
       <c r="A419" t="s">
         <v>134</v>
       </c>
@@ -8714,7 +8738,7 @@
       <c r="N419" s="3"/>
       <c r="O419" s="3"/>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:16" ns3:dyDescent="0.2">
       <c r="A420" t="s">
         <v>179</v>
       </c>
@@ -8743,7 +8767,7 @@
       <c r="N420" s="3"/>
       <c r="O420" s="3"/>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:16" ns3:dyDescent="0.2">
       <c r="A421" t="s">
         <v>169</v>
       </c>
@@ -8772,7 +8796,7 @@
       <c r="N421" s="3"/>
       <c r="O421" s="3"/>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:16" ns3:dyDescent="0.2">
       <c r="A422" t="s">
         <v>261</v>
       </c>
@@ -8801,7 +8825,7 @@
       <c r="N422" s="3"/>
       <c r="O422" s="3"/>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:16" ns3:dyDescent="0.2">
       <c r="A423" t="s">
         <v>162</v>
       </c>
@@ -8830,7 +8854,7 @@
       <c r="N423" s="3"/>
       <c r="O423" s="3"/>
     </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:16" ns3:dyDescent="0.2">
       <c r="A424" t="s">
         <v>226</v>
       </c>
@@ -8859,7 +8883,7 @@
       <c r="N424" s="3"/>
       <c r="O424" s="3"/>
     </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:16" ns3:dyDescent="0.2">
       <c r="A425" t="s">
         <v>195</v>
       </c>
@@ -8888,7 +8912,7 @@
       <c r="N425" s="3"/>
       <c r="O425" s="3"/>
     </row>
-    <row r="426" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:16" ns3:dyDescent="0.2">
       <c r="I426" s="3"/>
       <c r="J426" s="3"/>
       <c r="K426" s="3"/>
@@ -8897,7 +8921,7 @@
       <c r="N426" s="3"/>
       <c r="O426" s="3"/>
     </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:16" ns3:dyDescent="0.2">
       <c r="A427" s="1" t="s">
         <v>1</v>
       </c>
@@ -8908,7 +8932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:16" ns3:dyDescent="0.2">
       <c r="A428" t="s">
         <v>3</v>
       </c>
@@ -8919,15 +8943,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:16" ns3:dyDescent="0.2">
       <c r="A429" t="s">
         <v>6</v>
       </c>
-      <c r="B429" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" spans="1:16" ns3:dyDescent="0.2">
       <c r="A430" t="s">
         <v>5</v>
       </c>
@@ -8938,7 +8964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:16" ns3:dyDescent="0.2">
       <c r="A431" t="s">
         <v>7</v>
       </c>
@@ -8946,7 +8972,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:16" ns3:dyDescent="0.2">
       <c r="A432" t="s">
         <v>8</v>
       </c>
@@ -8957,7 +8983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:14" ns3:dyDescent="0.2">
       <c r="A433" t="s">
         <v>9</v>
       </c>
@@ -8968,7 +8994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:14" ns3:dyDescent="0.2">
       <c r="A434" t="s">
         <v>11</v>
       </c>
@@ -8979,7 +9005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:14" ns3:dyDescent="0.2">
       <c r="A435" s="1" t="s">
         <v>12</v>
       </c>
@@ -8987,7 +9013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:14" ns3:dyDescent="0.2">
       <c r="A436" s="1" t="s">
         <v>13</v>
       </c>
@@ -9014,7 +9040,7 @@
       </c>
       <c r="I436" s="4"/>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:14" ns3:dyDescent="0.2">
       <c r="A437" t="str">
         <f>B427</f>
         <v>electricity supply, high voltage, from vanadium-redox flow battery system</v>
@@ -9043,12 +9069,12 @@
       <c r="M437" s="3"/>
       <c r="N437" s="3"/>
     </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:14" ns3:dyDescent="0.2">
       <c r="A438" t="s">
         <v>269</v>
       </c>
       <c r="B438">
-        <v>1.33</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="C438" t="s">
         <v>4</v>
@@ -9072,13 +9098,12 @@
       <c r="M438" s="3"/>
       <c r="N438" s="3"/>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:14" ns3:dyDescent="0.2">
       <c r="A439" t="s">
         <v>264</v>
       </c>
       <c r="B439" s="9">
-        <f>1/(49000000)</f>
-        <v>2.0408163265306123E-8</v>
+        <v>2.3999135363090813e-08</v>
       </c>
       <c r="C439" t="s">
         <v>4</v>
@@ -9092,17 +9117,18 @@
       <c r="G439" t="s">
         <v>260</v>
       </c>
-      <c r="H439" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>One installed system per reference lifetime delivered kWh, at 95% usable SOC; see reference design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" spans="1:14" ns3:dyDescent="0.2">
       <c r="A440" t="s">
         <v>265</v>
       </c>
       <c r="B440" s="9">
-        <f>1/(49000000)</f>
-        <v>2.0408163265306123E-8</v>
+        <v>2.3999135363090813e-08</v>
       </c>
       <c r="C440" t="s">
         <v>4</v>
@@ -9120,13 +9146,12 @@
         <v>268</v>
       </c>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:14" ns3:dyDescent="0.2">
       <c r="A441" t="s">
         <v>230</v>
       </c>
       <c r="B441" s="9">
-        <f>-0.41/1000</f>
-        <v>-4.0999999999999999E-4</v>
+        <v>-0.00048075067959343513</v>
       </c>
       <c r="C441" t="s">
         <v>4</v>
@@ -9144,13 +9169,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:14" ns3:dyDescent="0.2">
       <c r="A442" t="s">
         <v>236</v>
       </c>
       <c r="B442">
-        <f>-0.66/1000</f>
-        <v>-6.6E-4</v>
+        <v>-0.0007821078223477665</v>
       </c>
       <c r="C442" t="s">
         <v>4</v>
@@ -9168,13 +9192,12 @@
         <v>271</v>
       </c>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:14" ns3:dyDescent="0.2">
       <c r="A443" t="s">
         <v>238</v>
       </c>
       <c r="B443">
-        <f>-5.55/1000</f>
-        <v>-5.5500000000000002E-3</v>
+        <v>-0.006533044628540581</v>
       </c>
       <c r="C443" t="s">
         <v>4</v>
@@ -9192,13 +9215,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:14" ns3:dyDescent="0.2">
       <c r="A444" t="s">
         <v>240</v>
       </c>
       <c r="B444">
-        <f>-0.1/1000</f>
-        <v>-1E-4</v>
+        <v>-0.00012299556873584042</v>
       </c>
       <c r="C444" t="s">
         <v>4</v>
@@ -9216,7 +9238,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:14" ns3:dyDescent="0.2">
       <c r="A446" s="1" t="s">
         <v>1</v>
       </c>
@@ -9224,7 +9246,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:14" ns3:dyDescent="0.2">
       <c r="A447" t="s">
         <v>3</v>
       </c>
@@ -9232,15 +9254,17 @@
         <v>28</v>
       </c>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:14" ns3:dyDescent="0.2">
       <c r="A448" t="s">
         <v>6</v>
       </c>
-      <c r="B448" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" spans="1:9" ns3:dyDescent="0.2">
       <c r="A449" t="s">
         <v>5</v>
       </c>
@@ -9248,7 +9272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:9" ns3:dyDescent="0.2">
       <c r="A450" t="s">
         <v>7</v>
       </c>
@@ -9256,7 +9280,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:9" ns3:dyDescent="0.2">
       <c r="A451" t="s">
         <v>8</v>
       </c>
@@ -9264,7 +9288,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:9" ns3:dyDescent="0.2">
       <c r="A452" t="s">
         <v>9</v>
       </c>
@@ -9272,7 +9296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:9" ns3:dyDescent="0.2">
       <c r="A453" t="s">
         <v>11</v>
       </c>
@@ -9280,13 +9304,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:9" ns3:dyDescent="0.2">
       <c r="A454" s="1" t="s">
         <v>12</v>
       </c>
       <c r="I454" s="9"/>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:9" ns3:dyDescent="0.2">
       <c r="A455" s="1" t="s">
         <v>13</v>
       </c>
@@ -9312,7 +9336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:9" ns3:dyDescent="0.2">
       <c r="A456" t="str">
         <f>B446</f>
         <v>market for battery, redox-flow, Vanadium</v>
@@ -9335,13 +9359,12 @@
         <v>battery, redox-flow, Vanadium</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:9" ns3:dyDescent="0.2">
       <c r="A457" t="s">
         <v>264</v>
       </c>
       <c r="B457" s="9">
-        <f>1/319948</f>
-        <v>3.1255078950329427E-6</v>
+        <v>3.125488357555868e-06</v>
       </c>
       <c r="C457" t="s">
         <v>4</v>
@@ -9355,17 +9378,18 @@
       <c r="G457" t="s">
         <v>260</v>
       </c>
-      <c r="H457" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>319950 kg = sum of S1 component rows (printed total differs by 2 kg).</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" spans="1:9" ns3:dyDescent="0.2">
       <c r="A458" t="s">
         <v>265</v>
       </c>
       <c r="B458" s="9">
-        <f>1/319948</f>
-        <v>3.1255078950329427E-6</v>
+        <v>3.125488357555868e-06</v>
       </c>
       <c r="C458" t="s">
         <v>4</v>
@@ -9380,11 +9404,16 @@
         <v>266</v>
       </c>
       <c r="I458" s="9"/>
-    </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>One replacement stack over 20 years; reference installed mass is not doubled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" spans="1:9" ns3:dyDescent="0.2">
       <c r="B459" s="9"/>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:9" ns3:dyDescent="0.2">
       <c r="A461" s="1" t="s">
         <v>1</v>
       </c>
@@ -9392,7 +9421,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:9" ns3:dyDescent="0.2">
       <c r="A462" t="s">
         <v>3</v>
       </c>
@@ -9400,12 +9429,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:9" ns3:dyDescent="0.2">
       <c r="A463" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:9" ns3:dyDescent="0.2">
       <c r="A464" t="s">
         <v>5</v>
       </c>
@@ -9413,7 +9442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:8" ns3:dyDescent="0.2">
       <c r="A465" t="s">
         <v>7</v>
       </c>
@@ -9421,7 +9450,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:8" ns3:dyDescent="0.2">
       <c r="A466" t="s">
         <v>8</v>
       </c>
@@ -9429,7 +9458,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:8" ns3:dyDescent="0.2">
       <c r="A467" t="s">
         <v>9</v>
       </c>
@@ -9437,7 +9466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:8" ns3:dyDescent="0.2">
       <c r="A468" t="s">
         <v>11</v>
       </c>
@@ -9445,12 +9474,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:8" ns3:dyDescent="0.2">
       <c r="A469" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:8" ns3:dyDescent="0.2">
       <c r="A470" s="1" t="s">
         <v>13</v>
       </c>
@@ -9476,7 +9505,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:8" ns3:dyDescent="0.2">
       <c r="A471" t="str">
         <f>B461</f>
         <v>market for used redox-flow battery</v>
@@ -9499,13 +9528,12 @@
         <v>used redox-flow battery</v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:8" ns3:dyDescent="0.2">
       <c r="A472" t="s">
         <v>230</v>
       </c>
       <c r="B472" s="9">
-        <f>B441/$B$440*$B$457</f>
-        <v>-6.2791453611211814E-2</v>
+        <v>-0.06279145361121181</v>
       </c>
       <c r="C472" t="s">
         <v>4</v>
@@ -9520,12 +9548,11 @@
         <v>231</v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:8" ns3:dyDescent="0.2">
       <c r="A473" t="s">
         <v>236</v>
       </c>
       <c r="B473" s="9">
-        <f t="shared" ref="B473:B475" si="0">B442/$B$440*$B$457</f>
         <v>-0.10107892532536537</v>
       </c>
       <c r="C473" t="s">
@@ -9541,13 +9568,12 @@
         <v>237</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:8" ns3:dyDescent="0.2">
       <c r="A474" t="s">
         <v>238</v>
       </c>
       <c r="B474" s="9">
-        <f t="shared" si="0"/>
-        <v>-0.84998187205420872</v>
+        <v>-0.8499818720542087</v>
       </c>
       <c r="C474" t="s">
         <v>4</v>
@@ -9562,13 +9588,12 @@
         <v>239</v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:8" ns3:dyDescent="0.2">
       <c r="A475" t="s">
         <v>240</v>
       </c>
       <c r="B475" s="9">
-        <f t="shared" si="0"/>
-        <v>-1.531498868566142E-2</v>
+        <v>-0.01531498868566142</v>
       </c>
       <c r="C475" t="s">
         <v>4</v>
@@ -9583,9 +9608,300 @@
         <v>241</v>
       </c>
     </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>market for used redox-flow battery, Vanadium, reference design</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>used redox-flow battery, Vanadium, reference design</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B481">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change. Per kg nominal installed system; includes treatment of one replacement stack over 20 years. No substitution or recovery-credit changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>market for used redox-flow battery, Vanadium, reference design</t>
+        </is>
+      </c>
+      <c r="B486">
+        <v>-1</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E486"/>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>used redox-flow battery, Vanadium, reference design</t>
+        </is>
+      </c>
+      <c r="H486"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>treatment of stack, for VRFB system</t>
+        </is>
+      </c>
+      <c r="B487">
+        <v>-0.06260978277855915</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E487"/>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>used stack, for VRFB system</t>
+        </is>
+      </c>
+      <c r="H487"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>treatment of electrolyte tank, for VRFB system</t>
+        </is>
+      </c>
+      <c r="B488">
+        <v>-0.10185654008438819</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E488"/>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>used electrolyte tank, for VRFB system</t>
+        </is>
+      </c>
+      <c r="H488"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>treatment of electrolyte solution, for VRFB system</t>
+        </is>
+      </c>
+      <c r="B489">
+        <v>-0.8508204406938584</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E489"/>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>used electrolyte solution, for VRFB system</t>
+        </is>
+      </c>
+      <c r="H489"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>treatment of periphericals, for VRFB system</t>
+        </is>
+      </c>
+      <c r="B490">
+        <v>-0.016018127832473823</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E490"/>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>used periphericals, for VRFB system</t>
+        </is>
+      </c>
+      <c r="H490"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P444" xr:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}"/>
+  <autoFilter ref="A1:P444" ns2:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
 </worksheet>
 </file>
--- a/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
@@ -1600,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}">
-  <dimension ref="A1:H490"/>
+  <dimension ref="A1:P490"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="63" customWidth="1"/>
@@ -6770,8 +6770,12 @@
       <c r="A296" t="s">
         <v>6</v>
       </c>
-      <c r="B296" t="s">
-        <v>197</v>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>APPROVED VRFB CONTROLLER FINISHED-MASS NORMALIZATION, issue79,2026-10-18. Source inherited Weber etal2018 DOI10.1021/acs.est.8b02073 control-design proxy:0.18kgPP housing+0.68kgLCD+0.32kgcontrol electronics=1.18kg finished components per declared1kg controller. Injection moulding is a service, not another retained plastic mass. Adopt an explicit mass-normalized version of this same reference architecture: divide these three finished-component inputs and housing-moulding service by1.18, preserving their relative recipe, and keep the provider output1kg. This is an engineering correction of the contradictory kg basis, not proof the original study intended any one fraction to be different. No source basis supports deleting the display, setting a metal tozero or treating0.68kg as an invented0.0068kg typo. The original archive carries an unresolved remaining-error warning; it doesnot independently establish a complete modern VRFB controller design. Keep parent process-control mix0.91kg stack interface+0.09kg BMS perkg controls and system13kg controls as the selected installed mass budget, rather than multiplying system mass by1.18 and preserving the overallocated reference. This changes BMS-attributed ingredients by factor1/1.18 while the stack interface is unchanged. Original freight0.1tkm lorry and0.6tkm rail remain route references per1kg delivered controller; no extra scaling of fixed route distance. Display supply includes its native upstream composition/processes and is not represented as bare indium or all precious metals. Exact LCD size,resolution,board topology,component metals,stock life and controller replacement intervals remain unverified source gaps. System electrolyte,stack replacement and installed energy capacity/lifetime are unchanged. No global native control/LCIA edits, no new recovery credit or primary-secondary-share claim.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Here, it is assumed that a monitoring system is required per stack and thus one BMS is required to control them. It must be noted that this is assumed to be major simplification, while the process control system is a relevant component. In fact, the modeling of the process control system is a crucial aspect since electronics potentially show high impacts in several categories. Therefore, this major gap needs to be fulfilled by future research.</t>
+        </is>
       </c>
     </row>
     <row r="297" spans="1:13" ns3:dyDescent="0.2">
@@ -6881,7 +6885,7 @@
         <v>210</v>
       </c>
       <c r="B304" s="3">
-        <v>0.18</v>
+        <v>0.15254237288135591</v>
       </c>
       <c r="C304" t="s">
         <v>28</v>
@@ -6904,7 +6908,7 @@
         <v>294</v>
       </c>
       <c r="B305" s="3">
-        <v>0.18</v>
+        <v>0.15254237288135591</v>
       </c>
       <c r="C305" t="s">
         <v>28</v>
@@ -6927,7 +6931,7 @@
         <v>222</v>
       </c>
       <c r="B306" s="3">
-        <v>0.68</v>
+        <v>0.576271186440678</v>
       </c>
       <c r="C306" t="s">
         <v>28</v>
@@ -6950,7 +6954,7 @@
         <v>223</v>
       </c>
       <c r="B307" s="3">
-        <v>0.32</v>
+        <v>0.27118644067796605</v>
       </c>
       <c r="C307" t="s">
         <v>28</v>

--- a/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
@@ -1600,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}">
-  <dimension ref="A1:P490"/>
+  <dimension ref="A1:P514"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="63" customWidth="1"/>
@@ -1656,8 +1656,12 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>APPROVED VRFB PFSA CHEMICAL IDENTITIES AND BALANCED SUPPLY, issue99, 2026-10-18. Weber2018 DOI10.1021/acs.est.8b02073 SI TableS2; balanced engineering reference approved inissue90 forfinishedEW1100acidPFSA. This appliesidenticalnetchemistrytotheexistingVRFB150kgmembrane/stack,notanadditionalmembrane layer. Original3.2kghexafluoroethane(C2F6)waslabelledhexafluoropropene(C3F6),and2.36kgSodiumchloratebiospherewaslabelledNaCl. Thesearechemicallydifferentmaterials. ReplaceoriginalunbalancedwholechemicalvectorbyonebalancedfinishedPFSAreferencefromissue90,notjustrenameC2F6whileleavingotherimbalances. EW1100,90%finishedretention,100%netintermediateconversion,10kgwater/kg,39.31MJheat+1kWh/kg aggregateallowances andallindustrialPFAS/purity/solvent/abatementgapsfromissue90apply. Productionoforiginalnafionmembrane remains1kg;retainoriginalfactory4e-10unitand0.87tkmlorry/5.22tkmtrain atwrapperonce. Nootheroriginalheat,rawchemicals,biosphereNaCl/NaOH/CO2orwastesremainonwrapper;newrefownsnetreaction/wastesonce.150kgfinishedmembraneinVRFBstackunchanged. Grossrawchemicalfeed changesbydesign,notbyrenormalizingallinputs. DedicatedproviderwithinexistingVRFBworkbookavoidsunresolvedcrossworkbookforwarddependency;identicalchemistryisnotdoublepurchased. GenericNaF-bearingWWTisnotdemonstratedfluorideabatement;uncertainPFASemissionsnotclaimedzeroindustrialemissions. No changesinvanadiumelectrolyte,hardwarecapacity,lifetimeorprimary-secondaryshares.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+The Vanadium Redox Flow Battery (VRFB) system is divided into two subsystems - a power and an energy sub-system - in accordance with the cell area related to the power and the electrolyte volume related to the energy storage capacity. Remaining components are assigned to the periphery. The considered VRFB system shows a rated power of 1 MW and an energy capacity of 8.3 MWh. The principal battery layout is derived from published literature, majorly a recent publication on stationary VRFB (Minke, C. Techno-ökonomische Modellierung Und Bewertung von Stationären, Vanadium-Redox-Flow-Batterien Im Industriellen Maßstab, 40th ed.; Cuvillier Verlag: Göttingen, 2016). The dimensions of the different parts provided there allow for calculating the battery composition on a mass basis. An 8.3 MWh system requires an electrolyte volume of 194 m3 and, assuming a void volume of 50%, a tank capacity of 300 m3. For a nominal power of 1 MW, two stacks with a total of 155 cells are required. Each stack is composed of a 105 membrane, a bipolar plates, two carbon felt electrodes, two current collector and the two associated gaskets.</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:15" ns3:dyDescent="0.2">
@@ -1754,28 +1758,45 @@
       <c r="G13" t="s">
         <v>19</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>APPROVED VRFB PFSA CHEMICAL IDENTITIES AND BALANCED SUPPLY, issue99, 2026-10-18. Weber2018 DOI10.1021/acs.est.8b02073 SI TableS2; balanced engineering reference approved inissue90 forfinishedEW1100acidPFSA. This appliesidenticalnetchemistrytotheexistingVRFB150kgmembrane/stack,notanadditionalmembrane layer. Original3.2kghexafluoroethane(C2F6)waslabelledhexafluoropropene(C3F6),and2.36kgSodiumchloratebiospherewaslabelledNaCl. Thesearechemicallydifferentmaterials. ReplaceoriginalunbalancedwholechemicalvectorbyonebalancedfinishedPFSAreferencefromissue90,notjustrenameC2F6whileleavingotherimbalances. EW1100,90%finishedretention,100%netintermediateconversion,10kgwater/kg,39.31MJheat+1kWh/kg aggregateallowances andallindustrialPFAS/purity/solvent/abatementgapsfromissue90apply. Productionoforiginalnafionmembrane remains1kg;retainoriginalfactory4e-10unitand0.87tkmlorry/5.22tkmtrain atwrapperonce. Nootheroriginalheat,rawchemicals,biosphereNaCl/NaOH/CO2orwastesremainonwrapper;newrefownsnetreaction/wastesonce.150kgfinishedmembraneinVRFBstackunchanged. Grossrawchemicalfeed changesbydesign,notbyrenormalizingallinputs. DedicatedproviderwithinexistingVRFBworkbookavoidsunresolvedcrossworkbookforwarddependency;identicalchemistryisnotdoublepurchased. GenericNaF-bearingWWTisnotdemonstratedfluorideabatement;uncertainPFASemissionsnotclaimedzeroindustrialemissions. No changesinvanadiumelectrolyte,hardwarecapacity,lifetimeorprimary-secondaryshares.</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>34</v>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+        </is>
       </c>
       <c r="B14" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED VRFB PFSA CHEMICAL IDENTITIES AND BALANCED SUPPLY, issue99, 2026-10-18. Weber2018 DOI10.1021/acs.est.8b02073 SI TableS2; balanced engineering reference approved inissue90 forfinishedEW1100acidPFSA. This appliesidenticalnetchemistrytotheexistingVRFB150kgmembrane/stack,notanadditionalmembrane layer. Original3.2kghexafluoroethane(C2F6)waslabelledhexafluoropropene(C3F6),and2.36kgSodiumchloratebiospherewaslabelledNaCl. Thesearechemicallydifferentmaterials. ReplaceoriginalunbalancedwholechemicalvectorbyonebalancedfinishedPFSAreferencefromissue90,notjustrenameC2F6whileleavingotherimbalances. EW1100,90%finishedretention,100%netintermediateconversion,10kgwater/kg,39.31MJheat+1kWh/kg aggregateallowances andallindustrialPFAS/purity/solvent/abatementgapsfromissue90apply. Productionoforiginalnafionmembrane remains1kg;retainoriginalfactory4e-10unitand0.87tkmlorry/5.22tkmtrain atwrapperonce. Nootheroriginalheat,rawchemicals,biosphereNaCl/NaOH/CO2orwastesremainonwrapper;newrefownsnetreaction/wastesonce.150kgfinishedmembraneinVRFBstackunchanged. Grossrawchemicalfeed changesbydesign,notbyrenormalizingallinputs. DedicatedproviderwithinexistingVRFBworkbookavoidsunresolvedcrossworkbookforwarddependency;identicalchemistryisnotdoublepurchased. GenericNaF-bearingWWTisnotdemonstratedfluorideabatement;uncertainPFASemissionsnotclaimedzeroindustrialemissions. No changesinvanadiumelectrolyte,hardwarecapacity,lifetimeorprimary-secondaryshares.</t>
+        </is>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -1786,129 +1807,59 @@
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="5"/>
+      <c r="C15"/>
+      <c r="D15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
       <c r="I15" s="4"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
     </row>
     <row r="16" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="A16" s="3"/>
+      <c r="B16" s="5"/>
+      <c r="C16"/>
+      <c r="D16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
     <row r="17" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B17" s="5">
-        <v>3</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="A17" s="3"/>
+      <c r="B17" s="5"/>
+      <c r="C17"/>
+      <c r="D17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
     <row r="18" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B18" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="5"/>
+      <c r="C18"/>
+      <c r="D18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="A19" s="3"/>
+      <c r="B19" s="5"/>
+      <c r="C19"/>
+      <c r="D19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
@@ -1938,27 +1889,13 @@
       <c r="N20" s="3"/>
     </row>
     <row r="21" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B21" s="5">
-        <v>39.31</v>
-      </c>
-      <c r="C21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="A21" s="3"/>
+      <c r="B21" s="5"/>
+      <c r="C21"/>
+      <c r="D21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
     </row>
@@ -2012,48 +1949,24 @@
       <c r="N23" s="3"/>
     </row>
     <row r="24" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B24" s="3">
-        <v>2.36</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>43</v>
-      </c>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24"/>
+      <c r="F24" s="3"/>
+      <c r="H24" s="3"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
       <c r="K24" s="4"/>
       <c r="O24" s="3"/>
     </row>
     <row r="25" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="3">
-        <v>1.87</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25"/>
+      <c r="F25" s="3"/>
+      <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
@@ -2062,24 +1975,12 @@
       <c r="N25" s="3"/>
     </row>
     <row r="26" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="6">
-        <v>8.8800000000000004E-2</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="A26" s="3"/>
+      <c r="B26" s="6"/>
+      <c r="D26" s="3"/>
+      <c r="E26"/>
+      <c r="F26" s="3"/>
+      <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -2088,27 +1989,13 @@
       <c r="N26" s="3"/>
     </row>
     <row r="27" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B27" s="3">
-        <v>-2.81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>46</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27"/>
+      <c r="D27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -2117,27 +2004,13 @@
       <c r="N27" s="3"/>
     </row>
     <row r="28" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B28" s="3">
-        <v>-0.11</v>
-      </c>
-      <c r="C28" t="s">
-        <v>290</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28"/>
+      <c r="D28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
@@ -2146,27 +2019,13 @@
       <c r="N28" s="3"/>
     </row>
     <row r="29" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B29" s="3">
-        <v>-0.38</v>
-      </c>
-      <c r="C29" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29"/>
+      <c r="D29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="3"/>
@@ -9903,6 +9762,592 @@
       </c>
       <c r="H490"/>
     </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B495">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Weber2018 DOI10.1021/acs.est.8b02073 SI TableS2; balanced engineering reference approved inissue90 forfinishedEW1100acidPFSA. This appliesidenticalnetchemistrytotheexistingVRFB150kgmembrane/stack,notanadditionalmembrane layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>APPROVED VRFB PFSA CHEMICAL IDENTITIES AND BALANCED SUPPLY, issue99, 2026-10-18. Weber2018 DOI10.1021/acs.est.8b02073 SI TableS2; balanced engineering reference approved inissue90 forfinishedEW1100acidPFSA. This appliesidenticalnetchemistrytotheexistingVRFB150kgmembrane/stack,notanadditionalmembrane layer. Original3.2kghexafluoroethane(C2F6)waslabelledhexafluoropropene(C3F6),and2.36kgSodiumchloratebiospherewaslabelledNaCl. Thesearechemicallydifferentmaterials. ReplaceoriginalunbalancedwholechemicalvectorbyonebalancedfinishedPFSAreferencefromissue90,notjustrenameC2F6whileleavingotherimbalances. EW1100,90%finishedretention,100%netintermediateconversion,10kgwater/kg,39.31MJheat+1kWh/kg aggregateallowances andallindustrialPFAS/purity/solvent/abatementgapsfromissue90apply. Productionoforiginalnafionmembrane remains1kg;retainoriginalfactory4e-10unitand0.87tkmlorry/5.22tkmtrain atwrapperonce. Nootheroriginalheat,rawchemicals,biosphereNaCl/NaOH/CO2orwastesremainonwrapper;newrefownsnetreaction/wastesonce.150kgfinishedmembraneinVRFBstackunchanged. Grossrawchemicalfeed changesbydesign,notbyrenormalizingallinputs. DedicatedproviderwithinexistingVRFBworkbookavoidsunresolvedcrossworkbookforwarddependency;identicalchemistryisnotdoublepurchased. GenericNaF-bearingWWTisnotdemonstratedfluorideabatement;uncertainPFASemissionsnotclaimedzeroindustrialemissions. No changesinvanadiumelectrolyte,hardwarecapacity,lifetimeorprimary-secondaryshares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+        </is>
+      </c>
+      <c r="B502">
+        <v>1</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>market for tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="B503">
+        <v>1.0666093025141414</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>market for sulfur trioxide</t>
+        </is>
+      </c>
+      <c r="B504">
+        <v>0.08086565656565657</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>sulfur trioxide</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>sulfur trioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>market for sodium hypochlorite, without water, in 15% solution state</t>
+        </is>
+      </c>
+      <c r="B505">
+        <v>0.15038135208080808</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>sodium hypochlorite, without water, in 15% solution state</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>sodium hypochlorite, without water, in 15% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>market for soda ash, dense</t>
+        </is>
+      </c>
+      <c r="B506">
+        <v>0.10705811975757576</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>soda ash, dense</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>soda ash, dense</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>market for sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="B507">
+        <v>0.0808015541010101</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>market for hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+      <c r="B508">
+        <v>0.03682626262626263</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>market for tap water</t>
+        </is>
+      </c>
+      <c r="B509">
+        <v>10</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B510">
+        <v>-0.010322524065827272</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>treatment of waste plastic, mixture, municipal incineration</t>
+        </is>
+      </c>
+      <c r="B511">
+        <v>-0.11111111111111116</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B512">
+        <v>39.31</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B513">
+        <v>1</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B514">
+        <v>0.08890707070707071</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P444" ns2:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
@@ -1600,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}">
-  <dimension ref="A1:P514"/>
+  <dimension ref="A1:P591"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="63" customWidth="1"/>
@@ -4556,8 +4556,18 @@
       <c r="A174" t="s">
         <v>6</v>
       </c>
-      <c r="B174" t="s">
-        <v>150</v>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
+Replace the chemically incompatible 0.33kg each of hexafluoroethane gas, TFE monomer and polyvinylfluoride perkg gasket. Adopt the published FE5540-type terpolymer reference at monomer massfractions {'VDF': 0.5926861629718567, 'HFP': 0.29622824511137696, 'TFE': 0.11108559191676634}, converted from molar fractions, rather than equal mass thirds. Finished compounded gasket formulation uses100/139 commercial-grade FKM,30/139 carbonblack,6/139 hydratedlime and3/139 MgO by mass. The source recipe demonstrates a cured compound, not a measured VRFB gasket. Retain installed gasket mass and all consumer allocations, including organic/hybrid flow-battery consumers of this shared provider.
+The commercial grade contains unspecified incorporated cure ingredients. Partition99% to modeled terpolymer and1% to a generic organic-chemical cure-package allowance. This1% is an explicit engineering coverage proxy, not published FE5540 assay, not a claim of metal-free catalyst/accelerator composition, and not bisphenol-A substituted for bisphenol-AF. Sensitivity0-3% incorporated package required. Do not add an extra full resin mass. FKM polymerization1kWh+6MJ/kg and10kg processwater/kg are engineering allowances;95% polymer retention assigns5% handling/unrecovered monomers to captured hazardous waste. Actual initiator/emulsifier/catalyst doses, fluorinated fugitives, purification and end groups remain gaps;100% capture is an inventory reference, not measured control efficiency.
+Because VDF is absent from older supported ecoinvent versions, define one common net route from vinylchloride through111TCA/142b toVDF: VC+Cl2+2HF -&gt;VDF+3HCl. Internal hydrochlorination HCl cancels from net feed. Scrub net HCl with3NaOH -&gt;3NaCl+3H2O. Reference feedkg perkg finishedVDF={'vinyl_chloride': 1.0273360213347598, 'chlorine': 1.165484573614863, 'HF': 0.6577476519039802, 'NaOH': 1.9724520842146482, 'water': 20.0}; rejectVDF=0.05263157894736836kg; brine=23.770388752120883kg at1100kg/m3. Assume95% finishedVDF retention after complete net conversion/recycle, not95% one-pass selectivity; generic brine WWT is not demonstrated salt removal. Use2kWh+10MJ/kgVDF and1gAlCl3/kgVDF catalyst-makeup allowance with equal collected spentcatalyst mass; these are engineering utilities/makeup, not patent measured plant inventory. Catalytic fluorination chemistry and commercial purification may require additional reagents; no certified commodity inventory is claimed. Chlorinated-gas fugitives are unresolved, not proven zero. Sensitivity catalyst0.1-10g/kg andutilities0.5-3x.
+HFP uses net3TFE-&gt;2HFP,95% netretention with captured reject,1kWh+6MJ/kg. These are explicit recirculated-net assumptions, not single-pass conversion from the patent. No hexafluoroethane feed remains. Polymer C/H/F balance closes before unspecified auxiliary ingredients.
+Finished compounding/presscure uses1kWh+6MJ/kg; the source177C presscure/230C postcure establishes process type but not industrial energy. Keep100% final compounded mass as a reference; source postcure masschanges and actual yields remain uncertain. Remove the previous pipe-extrusion proxy, retain original freight distances. No additional whole-gasket disposal is added because existing stack EOL handles the gasket; its generic fluoropolymer treatment remains a separate gap. No native/runtime or primary/secondary edits.
+NaOH input is in kg active solute supplied as50% solution: its 1.9724520842146482kg carrierwater is included within20kg total scrubber dilutionwater, so fresh tapwater is20-1.9724520842146482=18.02754791578535kg. Do not purchase the carrierwater a second time or omit it from the physical brine balance.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+FKM gaskets represent the first modeled variant. An important type of FKM is the terpolymer consisting of vinylidene fluoride (VDF), hexafluoropropylene (HFP) and tetrafluoroethylene (TFE). The respective ecoinvent datasets of the chemicals are used in which HFE is approximated by HFP and VFD by polyvinyl fluoride. As a forming process, the reference process “extrusion, plastic pipes” is used.</t>
+        </is>
       </c>
     </row>
     <row r="175" spans="1:13" ns3:dyDescent="0.2">
@@ -4657,98 +4667,85 @@
         <f>B176</f>
         <v>gasket, FKM</v>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
+Replace the chemically incompatible 0.33kg each of hexafluoroethane gas, TFE monomer and polyvinylfluoride perkg gasket. Adopt the published FE5540-type terpolymer reference at monomer massfractions {'VDF': 0.5926861629718567, 'HFP': 0.29622824511137696, 'TFE': 0.11108559191676634}, converted from molar fractions, rather than equal mass thirds. Finished compounded gasket formulation uses100/139 commercial-grade FKM,30/139 carbonblack,6/139 hydratedlime and3/139 MgO by mass. The source recipe demonstrates a cured compound, not a measured VRFB gasket. Retain installed gasket mass and all consumer allocations, including organic/hybrid flow-battery consumers of this shared provider.
+The commercial grade contains unspecified incorporated cure ingredients. Partition99% to modeled terpolymer and1% to a generic organic-chemical cure-package allowance. This1% is an explicit engineering coverage proxy, not published FE5540 assay, not a claim of metal-free catalyst/accelerator composition, and not bisphenol-A substituted for bisphenol-AF. Sensitivity0-3% incorporated package required. Do not add an extra full resin mass. FKM polymerization1kWh+6MJ/kg and10kg processwater/kg are engineering allowances;95% polymer retention assigns5% handling/unrecovered monomers to captured hazardous waste. Actual initiator/emulsifier/catalyst doses, fluorinated fugitives, purification and end groups remain gaps;100% capture is an inventory reference, not measured control efficiency.
+Because VDF is absent from older supported ecoinvent versions, define one common net route from vinylchloride through111TCA/142b toVDF: VC+Cl2+2HF -&gt;VDF+3HCl. Internal hydrochlorination HCl cancels from net feed. Scrub net HCl with3NaOH -&gt;3NaCl+3H2O. Reference feedkg perkg finishedVDF={'vinyl_chloride': 1.0273360213347598, 'chlorine': 1.165484573614863, 'HF': 0.6577476519039802, 'NaOH': 1.9724520842146482, 'water': 20.0}; rejectVDF=0.05263157894736836kg; brine=23.770388752120883kg at1100kg/m3. Assume95% finishedVDF retention after complete net conversion/recycle, not95% one-pass selectivity; generic brine WWT is not demonstrated salt removal. Use2kWh+10MJ/kgVDF and1gAlCl3/kgVDF catalyst-makeup allowance with equal collected spentcatalyst mass; these are engineering utilities/makeup, not patent measured plant inventory. Catalytic fluorination chemistry and commercial purification may require additional reagents; no certified commodity inventory is claimed. Chlorinated-gas fugitives are unresolved, not proven zero. Sensitivity catalyst0.1-10g/kg andutilities0.5-3x.
+HFP uses net3TFE-&gt;2HFP,95% netretention with captured reject,1kWh+6MJ/kg. These are explicit recirculated-net assumptions, not single-pass conversion from the patent. No hexafluoroethane feed remains. Polymer C/H/F balance closes before unspecified auxiliary ingredients.
+Finished compounding/presscure uses1kWh+6MJ/kg; the source177C presscure/230C postcure establishes process type but not industrial energy. Keep100% final compounded mass as a reference; source postcure masschanges and actual yields remain uncertain. Remove the previous pipe-extrusion proxy, retain original freight distances. No additional whole-gasket disposal is added because existing stack EOL handles the gasket; its generic fluoropolymer treatment remains a separate gap. No native/runtime or primary/secondary edits.
+NaOH input is in kg active solute supplied as50% solution: its 1.9724520842146482kg carrierwater is included within20kg total scrubber dilutionwater, so fresh tapwater is20-1.9724520842146482=18.02754791578535kg. Do not purchase the carrierwater a second time or omit it from the physical brine balance.</t>
+        </is>
+      </c>
     </row>
     <row r="182" spans="1:13" ns3:dyDescent="0.2">
-      <c r="A182" s="3" t="s">
-        <v>156</v>
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+        </is>
       </c>
       <c r="B182" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="C182" t="s">
-        <v>28</v>
-      </c>
-      <c r="D182" t="s">
-        <v>31</v>
-      </c>
-      <c r="F182" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H182" s="3" t="s">
-        <v>151</v>
+        <v>1</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+        </is>
+      </c>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
+Replace the chemically incompatible 0.33kg each of hexafluoroethane gas, TFE monomer and polyvinylfluoride perkg gasket. Adopt the published FE5540-type terpolymer reference at monomer massfractions {'VDF': 0.5926861629718567, 'HFP': 0.29622824511137696, 'TFE': 0.11108559191676634}, converted from molar fractions, rather than equal mass thirds. Finished compounded gasket formulation uses100/139 commercial-grade FKM,30/139 carbonblack,6/139 hydratedlime and3/139 MgO by mass. The source recipe demonstrates a cured compound, not a measured VRFB gasket. Retain installed gasket mass and all consumer allocations, including organic/hybrid flow-battery consumers of this shared provider.
+The commercial grade contains unspecified incorporated cure ingredients. Partition99% to modeled terpolymer and1% to a generic organic-chemical cure-package allowance. This1% is an explicit engineering coverage proxy, not published FE5540 assay, not a claim of metal-free catalyst/accelerator composition, and not bisphenol-A substituted for bisphenol-AF. Sensitivity0-3% incorporated package required. Do not add an extra full resin mass. FKM polymerization1kWh+6MJ/kg and10kg processwater/kg are engineering allowances;95% polymer retention assigns5% handling/unrecovered monomers to captured hazardous waste. Actual initiator/emulsifier/catalyst doses, fluorinated fugitives, purification and end groups remain gaps;100% capture is an inventory reference, not measured control efficiency.
+Because VDF is absent from older supported ecoinvent versions, define one common net route from vinylchloride through111TCA/142b toVDF: VC+Cl2+2HF -&gt;VDF+3HCl. Internal hydrochlorination HCl cancels from net feed. Scrub net HCl with3NaOH -&gt;3NaCl+3H2O. Reference feedkg perkg finishedVDF={'vinyl_chloride': 1.0273360213347598, 'chlorine': 1.165484573614863, 'HF': 0.6577476519039802, 'NaOH': 1.9724520842146482, 'water': 20.0}; rejectVDF=0.05263157894736836kg; brine=23.770388752120883kg at1100kg/m3. Assume95% finishedVDF retention after complete net conversion/recycle, not95% one-pass selectivity; generic brine WWT is not demonstrated salt removal. Use2kWh+10MJ/kgVDF and1gAlCl3/kgVDF catalyst-makeup allowance with equal collected spentcatalyst mass; these are engineering utilities/makeup, not patent measured plant inventory. Catalytic fluorination chemistry and commercial purification may require additional reagents; no certified commodity inventory is claimed. Chlorinated-gas fugitives are unresolved, not proven zero. Sensitivity catalyst0.1-10g/kg andutilities0.5-3x.
+HFP uses net3TFE-&gt;2HFP,95% netretention with captured reject,1kWh+6MJ/kg. These are explicit recirculated-net assumptions, not single-pass conversion from the patent. No hexafluoroethane feed remains. Polymer C/H/F balance closes before unspecified auxiliary ingredients.
+Finished compounding/presscure uses1kWh+6MJ/kg; the source177C presscure/230C postcure establishes process type but not industrial energy. Keep100% final compounded mass as a reference; source postcure masschanges and actual yields remain uncertain. Remove the previous pipe-extrusion proxy, retain original freight distances. No additional whole-gasket disposal is added because existing stack EOL handles the gasket; its generic fluoropolymer treatment remains a separate gap. No native/runtime or primary/secondary edits.
+NaOH input is in kg active solute supplied as50% solution: its 1.9724520842146482kg carrierwater is included within20kg total scrubber dilutionwater, so fresh tapwater is20-1.9724520842146482=18.02754791578535kg. Do not purchase the carrierwater a second time or omit it from the physical brine balance.</t>
+        </is>
       </c>
     </row>
     <row r="183" spans="1:13" ns3:dyDescent="0.2">
-      <c r="A183" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B183" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="C183" t="s">
-        <v>28</v>
-      </c>
-      <c r="D183" t="s">
-        <v>31</v>
-      </c>
-      <c r="F183" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G183" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H183" s="3" t="s">
-        <v>152</v>
-      </c>
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+      <c r="C183"/>
+      <c r="D183"/>
+      <c r="F183" s="3"/>
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
     </row>
     <row r="184" spans="1:13" ns3:dyDescent="0.2">
-      <c r="A184" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B184" s="3">
-        <v>0.33</v>
-      </c>
-      <c r="C184" t="s">
-        <v>28</v>
-      </c>
-      <c r="D184" t="s">
-        <v>31</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G184" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H184" s="3" t="s">
-        <v>153</v>
-      </c>
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+      <c r="C184"/>
+      <c r="D184"/>
+      <c r="F184" s="3"/>
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
     </row>
     <row r="185" spans="1:13" ns3:dyDescent="0.2">
-      <c r="A185" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B185" s="3">
-        <v>1</v>
-      </c>
-      <c r="C185" t="s">
-        <v>28</v>
-      </c>
-      <c r="D185" t="s">
-        <v>31</v>
-      </c>
-      <c r="F185" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G185" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H185" s="3" t="s">
-        <v>154</v>
-      </c>
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+      <c r="C185"/>
+      <c r="D185"/>
+      <c r="F185" s="3"/>
+      <c r="G185" s="3"/>
+      <c r="H185" s="3"/>
     </row>
     <row r="186" spans="1:13" ns3:dyDescent="0.2">
       <c r="A186" s="3" t="s">
@@ -10348,6 +10345,1729 @@
         </is>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B519">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
+Replace the chemically incompatible 0.33kg each of hexafluoroethane gas, TFE monomer and polyvinylfluoride perkg gasket. Adopt the published FE5540-type terpolymer reference at monomer massfractions {'VDF': 0.5926861629718567, 'HFP': 0.29622824511137696, 'TFE': 0.11108559191676634}, converted from molar fractions, rather than equal mass thirds. Finished compounded gasket formulation uses100/139 commercial-grade FKM,30/139 carbonblack,6/139 hydratedlime and3/139 MgO by mass. The source recipe demonstrates a cured compound, not a measured VRFB gasket. Retain installed gasket mass and all consumer allocations, including organic/hybrid flow-battery consumers of this shared provider.
+The commercial grade contains unspecified incorporated cure ingredients. Partition99% to modeled terpolymer and1% to a generic organic-chemical cure-package allowance. This1% is an explicit engineering coverage proxy, not published FE5540 assay, not a claim of metal-free catalyst/accelerator composition, and not bisphenol-A substituted for bisphenol-AF. Sensitivity0-3% incorporated package required. Do not add an extra full resin mass. FKM polymerization1kWh+6MJ/kg and10kg processwater/kg are engineering allowances;95% polymer retention assigns5% handling/unrecovered monomers to captured hazardous waste. Actual initiator/emulsifier/catalyst doses, fluorinated fugitives, purification and end groups remain gaps;100% capture is an inventory reference, not measured control efficiency.
+Because VDF is absent from older supported ecoinvent versions, define one common net route from vinylchloride through111TCA/142b toVDF: VC+Cl2+2HF -&gt;VDF+3HCl. Internal hydrochlorination HCl cancels from net feed. Scrub net HCl with3NaOH -&gt;3NaCl+3H2O. Reference feedkg perkg finishedVDF={'vinyl_chloride': 1.0273360213347598, 'chlorine': 1.165484573614863, 'HF': 0.6577476519039802, 'NaOH': 1.9724520842146482, 'water': 20.0}; rejectVDF=0.05263157894736836kg; brine=23.770388752120883kg at1100kg/m3. Assume95% finishedVDF retention after complete net conversion/recycle, not95% one-pass selectivity; generic brine WWT is not demonstrated salt removal. Use2kWh+10MJ/kgVDF and1gAlCl3/kgVDF catalyst-makeup allowance with equal collected spentcatalyst mass; these are engineering utilities/makeup, not patent measured plant inventory. Catalytic fluorination chemistry and commercial purification may require additional reagents; no certified commodity inventory is claimed. Chlorinated-gas fugitives are unresolved, not proven zero. Sensitivity catalyst0.1-10g/kg andutilities0.5-3x.
+HFP uses net3TFE-&gt;2HFP,95% netretention with captured reject,1kWh+6MJ/kg. These are explicit recirculated-net assumptions, not single-pass conversion from the patent. No hexafluoroethane feed remains. Polymer C/H/F balance closes before unspecified auxiliary ingredients.
+Finished compounding/presscure uses1kWh+6MJ/kg; the source177C presscure/230C postcure establishes process type but not industrial energy. Keep100% final compounded mass as a reference; source postcure masschanges and actual yields remain uncertain. Remove the previous pipe-extrusion proxy, retain original freight distances. No additional whole-gasket disposal is added because existing stack EOL handles the gasket; its generic fluoropolymer treatment remains a separate gap. No native/runtime or primary/secondary edits.
+NaOH input is in kg active solute supplied as50% solution: its 1.9724520842146482kg carrierwater is included within20kg total scrubber dilutionwater, so fresh tapwater is20-1.9724520842146482=18.02754791578535kg. Do not purchase the carrierwater a second time or omit it from the physical brine balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+        </is>
+      </c>
+      <c r="B526">
+        <v>1</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>market for vinyl chloride</t>
+        </is>
+      </c>
+      <c r="B527">
+        <v>1.0273360213347598</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>vinyl chloride</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>vinyl chloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>market for chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="B528">
+        <v>1.165484573614863</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>market for hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="B529">
+        <v>0.6577476519039802</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>hydrogen fluoride</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>hydrogen fluoride</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>market for sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="B530">
+        <v>1.9724520842146482</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>market for tap water</t>
+        </is>
+      </c>
+      <c r="B531">
+        <v>18.02754791578535</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>market for aluminium chloride</t>
+        </is>
+      </c>
+      <c r="B532">
+        <v>0.001</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>aluminium chloride</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>aluminium chloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B533">
+        <v>-0.053631578947368364</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B534">
+        <v>-0.021609444320109895</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B535">
+        <v>2</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B536">
+        <v>10</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B541">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
+Replace the chemically incompatible 0.33kg each of hexafluoroethane gas, TFE monomer and polyvinylfluoride perkg gasket. Adopt the published FE5540-type terpolymer reference at monomer massfractions {'VDF': 0.5926861629718567, 'HFP': 0.29622824511137696, 'TFE': 0.11108559191676634}, converted from molar fractions, rather than equal mass thirds. Finished compounded gasket formulation uses100/139 commercial-grade FKM,30/139 carbonblack,6/139 hydratedlime and3/139 MgO by mass. The source recipe demonstrates a cured compound, not a measured VRFB gasket. Retain installed gasket mass and all consumer allocations, including organic/hybrid flow-battery consumers of this shared provider.
+The commercial grade contains unspecified incorporated cure ingredients. Partition99% to modeled terpolymer and1% to a generic organic-chemical cure-package allowance. This1% is an explicit engineering coverage proxy, not published FE5540 assay, not a claim of metal-free catalyst/accelerator composition, and not bisphenol-A substituted for bisphenol-AF. Sensitivity0-3% incorporated package required. Do not add an extra full resin mass. FKM polymerization1kWh+6MJ/kg and10kg processwater/kg are engineering allowances;95% polymer retention assigns5% handling/unrecovered monomers to captured hazardous waste. Actual initiator/emulsifier/catalyst doses, fluorinated fugitives, purification and end groups remain gaps;100% capture is an inventory reference, not measured control efficiency.
+Because VDF is absent from older supported ecoinvent versions, define one common net route from vinylchloride through111TCA/142b toVDF: VC+Cl2+2HF -&gt;VDF+3HCl. Internal hydrochlorination HCl cancels from net feed. Scrub net HCl with3NaOH -&gt;3NaCl+3H2O. Reference feedkg perkg finishedVDF={'vinyl_chloride': 1.0273360213347598, 'chlorine': 1.165484573614863, 'HF': 0.6577476519039802, 'NaOH': 1.9724520842146482, 'water': 20.0}; rejectVDF=0.05263157894736836kg; brine=23.770388752120883kg at1100kg/m3. Assume95% finishedVDF retention after complete net conversion/recycle, not95% one-pass selectivity; generic brine WWT is not demonstrated salt removal. Use2kWh+10MJ/kgVDF and1gAlCl3/kgVDF catalyst-makeup allowance with equal collected spentcatalyst mass; these are engineering utilities/makeup, not patent measured plant inventory. Catalytic fluorination chemistry and commercial purification may require additional reagents; no certified commodity inventory is claimed. Chlorinated-gas fugitives are unresolved, not proven zero. Sensitivity catalyst0.1-10g/kg andutilities0.5-3x.
+HFP uses net3TFE-&gt;2HFP,95% netretention with captured reject,1kWh+6MJ/kg. These are explicit recirculated-net assumptions, not single-pass conversion from the patent. No hexafluoroethane feed remains. Polymer C/H/F balance closes before unspecified auxiliary ingredients.
+Finished compounding/presscure uses1kWh+6MJ/kg; the source177C presscure/230C postcure establishes process type but not industrial energy. Keep100% final compounded mass as a reference; source postcure masschanges and actual yields remain uncertain. Remove the previous pipe-extrusion proxy, retain original freight distances. No additional whole-gasket disposal is added because existing stack EOL handles the gasket; its generic fluoropolymer treatment remains a separate gap. No native/runtime or primary/secondary edits.
+NaOH input is in kg active solute supplied as50% solution: its 1.9724520842146482kg carrierwater is included within20kg total scrubber dilutionwater, so fresh tapwater is20-1.9724520842146482=18.02754791578535kg. Do not purchase the carrierwater a second time or omit it from the physical brine balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+        </is>
+      </c>
+      <c r="B548">
+        <v>1</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>market for tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="B549">
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B550">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B551">
+        <v>1</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B552">
+        <v>6</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B557">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
+Replace the chemically incompatible 0.33kg each of hexafluoroethane gas, TFE monomer and polyvinylfluoride perkg gasket. Adopt the published FE5540-type terpolymer reference at monomer massfractions {'VDF': 0.5926861629718567, 'HFP': 0.29622824511137696, 'TFE': 0.11108559191676634}, converted from molar fractions, rather than equal mass thirds. Finished compounded gasket formulation uses100/139 commercial-grade FKM,30/139 carbonblack,6/139 hydratedlime and3/139 MgO by mass. The source recipe demonstrates a cured compound, not a measured VRFB gasket. Retain installed gasket mass and all consumer allocations, including organic/hybrid flow-battery consumers of this shared provider.
+The commercial grade contains unspecified incorporated cure ingredients. Partition99% to modeled terpolymer and1% to a generic organic-chemical cure-package allowance. This1% is an explicit engineering coverage proxy, not published FE5540 assay, not a claim of metal-free catalyst/accelerator composition, and not bisphenol-A substituted for bisphenol-AF. Sensitivity0-3% incorporated package required. Do not add an extra full resin mass. FKM polymerization1kWh+6MJ/kg and10kg processwater/kg are engineering allowances;95% polymer retention assigns5% handling/unrecovered monomers to captured hazardous waste. Actual initiator/emulsifier/catalyst doses, fluorinated fugitives, purification and end groups remain gaps;100% capture is an inventory reference, not measured control efficiency.
+Because VDF is absent from older supported ecoinvent versions, define one common net route from vinylchloride through111TCA/142b toVDF: VC+Cl2+2HF -&gt;VDF+3HCl. Internal hydrochlorination HCl cancels from net feed. Scrub net HCl with3NaOH -&gt;3NaCl+3H2O. Reference feedkg perkg finishedVDF={'vinyl_chloride': 1.0273360213347598, 'chlorine': 1.165484573614863, 'HF': 0.6577476519039802, 'NaOH': 1.9724520842146482, 'water': 20.0}; rejectVDF=0.05263157894736836kg; brine=23.770388752120883kg at1100kg/m3. Assume95% finishedVDF retention after complete net conversion/recycle, not95% one-pass selectivity; generic brine WWT is not demonstrated salt removal. Use2kWh+10MJ/kgVDF and1gAlCl3/kgVDF catalyst-makeup allowance with equal collected spentcatalyst mass; these are engineering utilities/makeup, not patent measured plant inventory. Catalytic fluorination chemistry and commercial purification may require additional reagents; no certified commodity inventory is claimed. Chlorinated-gas fugitives are unresolved, not proven zero. Sensitivity catalyst0.1-10g/kg andutilities0.5-3x.
+HFP uses net3TFE-&gt;2HFP,95% netretention with captured reject,1kWh+6MJ/kg. These are explicit recirculated-net assumptions, not single-pass conversion from the patent. No hexafluoroethane feed remains. Polymer C/H/F balance closes before unspecified auxiliary ingredients.
+Finished compounding/presscure uses1kWh+6MJ/kg; the source177C presscure/230C postcure establishes process type but not industrial energy. Keep100% final compounded mass as a reference; source postcure masschanges and actual yields remain uncertain. Remove the previous pipe-extrusion proxy, retain original freight distances. No additional whole-gasket disposal is added because existing stack EOL handles the gasket; its generic fluoropolymer treatment remains a separate gap. No native/runtime or primary/secondary edits.
+NaOH input is in kg active solute supplied as50% solution: its 1.9724520842146482kg carrierwater is included within20kg total scrubber dilutionwater, so fresh tapwater is20-1.9724520842146482=18.02754791578535kg. Do not purchase the carrierwater a second time or omit it from the physical brine balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+        </is>
+      </c>
+      <c r="B564">
+        <v>1</v>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+        </is>
+      </c>
+      <c r="B565">
+        <v>0.6238801715493228</v>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+        </is>
+      </c>
+      <c r="B566">
+        <v>0.3118192053803968</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>market for tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="B567">
+        <v>0.11693220201764878</v>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B568">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B569">
+        <v>10</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B570">
+        <v>-0.01</v>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B571">
+        <v>1</v>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B572">
+        <v>6</v>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B577">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
+Replace the chemically incompatible 0.33kg each of hexafluoroethane gas, TFE monomer and polyvinylfluoride perkg gasket. Adopt the published FE5540-type terpolymer reference at monomer massfractions {'VDF': 0.5926861629718567, 'HFP': 0.29622824511137696, 'TFE': 0.11108559191676634}, converted from molar fractions, rather than equal mass thirds. Finished compounded gasket formulation uses100/139 commercial-grade FKM,30/139 carbonblack,6/139 hydratedlime and3/139 MgO by mass. The source recipe demonstrates a cured compound, not a measured VRFB gasket. Retain installed gasket mass and all consumer allocations, including organic/hybrid flow-battery consumers of this shared provider.
+The commercial grade contains unspecified incorporated cure ingredients. Partition99% to modeled terpolymer and1% to a generic organic-chemical cure-package allowance. This1% is an explicit engineering coverage proxy, not published FE5540 assay, not a claim of metal-free catalyst/accelerator composition, and not bisphenol-A substituted for bisphenol-AF. Sensitivity0-3% incorporated package required. Do not add an extra full resin mass. FKM polymerization1kWh+6MJ/kg and10kg processwater/kg are engineering allowances;95% polymer retention assigns5% handling/unrecovered monomers to captured hazardous waste. Actual initiator/emulsifier/catalyst doses, fluorinated fugitives, purification and end groups remain gaps;100% capture is an inventory reference, not measured control efficiency.
+Because VDF is absent from older supported ecoinvent versions, define one common net route from vinylchloride through111TCA/142b toVDF: VC+Cl2+2HF -&gt;VDF+3HCl. Internal hydrochlorination HCl cancels from net feed. Scrub net HCl with3NaOH -&gt;3NaCl+3H2O. Reference feedkg perkg finishedVDF={'vinyl_chloride': 1.0273360213347598, 'chlorine': 1.165484573614863, 'HF': 0.6577476519039802, 'NaOH': 1.9724520842146482, 'water': 20.0}; rejectVDF=0.05263157894736836kg; brine=23.770388752120883kg at1100kg/m3. Assume95% finishedVDF retention after complete net conversion/recycle, not95% one-pass selectivity; generic brine WWT is not demonstrated salt removal. Use2kWh+10MJ/kgVDF and1gAlCl3/kgVDF catalyst-makeup allowance with equal collected spentcatalyst mass; these are engineering utilities/makeup, not patent measured plant inventory. Catalytic fluorination chemistry and commercial purification may require additional reagents; no certified commodity inventory is claimed. Chlorinated-gas fugitives are unresolved, not proven zero. Sensitivity catalyst0.1-10g/kg andutilities0.5-3x.
+HFP uses net3TFE-&gt;2HFP,95% netretention with captured reject,1kWh+6MJ/kg. These are explicit recirculated-net assumptions, not single-pass conversion from the patent. No hexafluoroethane feed remains. Polymer C/H/F balance closes before unspecified auxiliary ingredients.
+Finished compounding/presscure uses1kWh+6MJ/kg; the source177C presscure/230C postcure establishes process type but not industrial energy. Keep100% final compounded mass as a reference; source postcure masschanges and actual yields remain uncertain. Remove the previous pipe-extrusion proxy, retain original freight distances. No additional whole-gasket disposal is added because existing stack EOL handles the gasket; its generic fluoropolymer treatment remains a separate gap. No native/runtime or primary/secondary edits.
+NaOH input is in kg active solute supplied as50% solution: its 1.9724520842146482kg carrierwater is included within20kg total scrubber dilutionwater, so fresh tapwater is20-1.9724520842146482=18.02754791578535kg. Do not purchase the carrierwater a second time or omit it from the physical brine balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+        </is>
+      </c>
+      <c r="B584">
+        <v>1</v>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+        </is>
+      </c>
+      <c r="B585">
+        <v>0.7122302158273381</v>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>market for chemical, organic</t>
+        </is>
+      </c>
+      <c r="B586">
+        <v>0.007194244604316547</v>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>chemical, organic</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>chemical, organic</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B587">
+        <v>0.2158273381294964</v>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>market for lime, hydrated, loose weight</t>
+        </is>
+      </c>
+      <c r="B588">
+        <v>0.04316546762589928</v>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>lime, hydrated, loose weight</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>lime, hydrated, loose weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>market for magnesium oxide</t>
+        </is>
+      </c>
+      <c r="B589">
+        <v>0.02158273381294964</v>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>magnesium oxide</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>magnesium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B590">
+        <v>1</v>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B591">
+        <v>6</v>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:P444" ns2:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
@@ -8389,7 +8389,13 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change.</t>
+          <t>APPROVED LARGE VRFB POWER-CONVERSION INTERFACE AUDIT, issue123, 2026-10-19. Weber2018 SI sections1.1 and1.4.4,TableS1:1MW,155cells total across two stacks, generic500kW PV inverter proxy. SMA Sunny Central Storage500/630/... manual SCS-BE-E7-en-12 section14.1:500kW battery converter430-850VDC,1900kg, bidirectional battery operation; https://files.sma.de/downloads/SCS-BE-E7-en-12.pdf . Manufacturer mass alone is not a material inventory.
+UNRESOLVED DC INTERFACE AND HARDWARE COMPOSITION: existing system purchases2 generic500kW photovoltaic inverters. Native supplier includes housing,bulkCu/Al/steel, electronics, factory energy, packaging and disposal; do not append another complete inverter or duplicate its EOL. Its PV function and tiny generic transistor input do not establish a complete rated bidirectional VRFB converter. Native500kW market description also says0.5kW in one paragraph, but production nameplate is500kW; do not apply an erroneous1000x correction from that text typo.
+The source has155 cells TOTAL across two stacks, not155 in each stack. With retained1.25V/cell nominal assumption, even all cells in electrical series give193.75V. A430V minimum commercial battery inverter cannot be directly supplied by that reference. At1MW, nominal input current would be about5161A before losses; actual discharge/charge voltage and current limits require SOC/duty data. The source does not establish a suitable series arrangement or a low-voltage DC/DC boost stage. Adding a normal high-voltage battery inverter alone does not resolve the interface.
+Required correction: a documented low-voltage bidirectional DC/DC stage plus AC stage, or a fully specified revised cell/stack series arrangement with consistent active area, bipolar plates, collectors and hardware counts. Needed masses include inductive/transformer magnetics, conductors, switches, controls, protection and cooling; lifetimes must be allocated consistently over the existing20-year service. Manufacturer1900kg product mass must not be spread into invented elemental fractions or linearly scaled to unknown low-voltage converter architecture. Current generic power-electronics/magnetics coverage and trace metals remain unvalidated.
+Retain numerical exchanges and existing roundtrip loss allocation while this engineering design is OPEN. Do not silently impose800V on the source stacks, buy155 extra cells without changing material geometry, claim two PV inverters prove battery charging coverage, or add conversion losses twice. This commit documents a quantified interface failure and required inventory rather than claiming system metal quantities are validated. No native/runtime/primarysecondary edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change.</t>
         </is>
       </c>
     </row>
@@ -8501,6 +8507,15 @@
       <c r="G416" t="str">
         <f>B411</f>
         <v>vanadium-redox flow battery system</v>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>APPROVED LARGE VRFB POWER-CONVERSION INTERFACE AUDIT, issue123, 2026-10-19. Weber2018 SI sections1.1 and1.4.4,TableS1:1MW,155cells total across two stacks, generic500kW PV inverter proxy. SMA Sunny Central Storage500/630/... manual SCS-BE-E7-en-12 section14.1:500kW battery converter430-850VDC,1900kg, bidirectional battery operation; https://files.sma.de/downloads/SCS-BE-E7-en-12.pdf . Manufacturer mass alone is not a material inventory.
+UNRESOLVED DC INTERFACE AND HARDWARE COMPOSITION: existing system purchases2 generic500kW photovoltaic inverters. Native supplier includes housing,bulkCu/Al/steel, electronics, factory energy, packaging and disposal; do not append another complete inverter or duplicate its EOL. Its PV function and tiny generic transistor input do not establish a complete rated bidirectional VRFB converter. Native500kW market description also says0.5kW in one paragraph, but production nameplate is500kW; do not apply an erroneous1000x correction from that text typo.
+The source has155 cells TOTAL across two stacks, not155 in each stack. With retained1.25V/cell nominal assumption, even all cells in electrical series give193.75V. A430V minimum commercial battery inverter cannot be directly supplied by that reference. At1MW, nominal input current would be about5161A before losses; actual discharge/charge voltage and current limits require SOC/duty data. The source does not establish a suitable series arrangement or a low-voltage DC/DC boost stage. Adding a normal high-voltage battery inverter alone does not resolve the interface.
+Required correction: a documented low-voltage bidirectional DC/DC stage plus AC stage, or a fully specified revised cell/stack series arrangement with consistent active area, bipolar plates, collectors and hardware counts. Needed masses include inductive/transformer magnetics, conductors, switches, controls, protection and cooling; lifetimes must be allocated consistently over the existing20-year service. Manufacturer1900kg product mass must not be spread into invented elemental fractions or linearly scaled to unknown low-voltage converter architecture. Current generic power-electronics/magnetics coverage and trace metals remain unvalidated.
+Retain numerical exchanges and existing roundtrip loss allocation while this engineering design is OPEN. Do not silently impose800V on the source stacks, buy155 extra cells without changing material geometry, claim two PV inverters prove battery charging coverage, or add conversion losses twice. This commit documents a quantified interface failure and required inventory rather than claiming system metal quantities are validated. No native/runtime/primarysecondary edits.</t>
+        </is>
       </c>
       <c r="I416" s="3"/>
       <c r="J416" s="3"/>
@@ -8675,8 +8690,14 @@
       <c r="G422" t="s">
         <v>262</v>
       </c>
-      <c r="H422" s="3" t="s">
-        <v>257</v>
+      <c r="H422" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED LARGE VRFB POWER-CONVERSION INTERFACE AUDIT, issue123, 2026-10-19. Weber2018 SI sections1.1 and1.4.4,TableS1:1MW,155cells total across two stacks, generic500kW PV inverter proxy. SMA Sunny Central Storage500/630/... manual SCS-BE-E7-en-12 section14.1:500kW battery converter430-850VDC,1900kg, bidirectional battery operation; https://files.sma.de/downloads/SCS-BE-E7-en-12.pdf . Manufacturer mass alone is not a material inventory.
+UNRESOLVED DC INTERFACE AND HARDWARE COMPOSITION: existing system purchases2 generic500kW photovoltaic inverters. Native supplier includes housing,bulkCu/Al/steel, electronics, factory energy, packaging and disposal; do not append another complete inverter or duplicate its EOL. Its PV function and tiny generic transistor input do not establish a complete rated bidirectional VRFB converter. Native500kW market description also says0.5kW in one paragraph, but production nameplate is500kW; do not apply an erroneous1000x correction from that text typo.
+The source has155 cells TOTAL across two stacks, not155 in each stack. With retained1.25V/cell nominal assumption, even all cells in electrical series give193.75V. A430V minimum commercial battery inverter cannot be directly supplied by that reference. At1MW, nominal input current would be about5161A before losses; actual discharge/charge voltage and current limits require SOC/duty data. The source does not establish a suitable series arrangement or a low-voltage DC/DC boost stage. Adding a normal high-voltage battery inverter alone does not resolve the interface.
+Required correction: a documented low-voltage bidirectional DC/DC stage plus AC stage, or a fully specified revised cell/stack series arrangement with consistent active area, bipolar plates, collectors and hardware counts. Needed masses include inductive/transformer magnetics, conductors, switches, controls, protection and cooling; lifetimes must be allocated consistently over the existing20-year service. Manufacturer1900kg product mass must not be spread into invented elemental fractions or linearly scaled to unknown low-voltage converter architecture. Current generic power-electronics/magnetics coverage and trace metals remain unvalidated.
+Retain numerical exchanges and existing roundtrip loss allocation while this engineering design is OPEN. Do not silently impose800V on the source stacks, buy155 extra cells without changing material geometry, claim two PV inverters prove battery charging coverage, or add conversion losses twice. This commit documents a quantified interface failure and required inventory rather than claiming system metal quantities are validated. No native/runtime/primarysecondary edits.</t>
+        </is>
       </c>
       <c r="I422" s="3"/>
       <c r="K422" s="3"/>

--- a/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
@@ -1767,7 +1767,7 @@
     <row r="14" spans="1:15" ns3:dyDescent="0.2">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+          <t xml:space="preserve">PFSA membrane production, vanadium redox-flow battery, EW1100</t>
         </is>
       </c>
       <c r="B14" s="5">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+          <t xml:space="preserve">PFSA membrane, vanadium redox-flow battery, EW1100</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -3438,7 +3438,7 @@
     <row r="109" spans="1:13" ns3:dyDescent="0.2">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>vanadium electrolyte conditioning, reference design</t>
+          <t xml:space="preserve">vanadium electrolyte conditioning</t>
         </is>
       </c>
       <c r="B109" s="3">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>vanadium electrolyte conditioning, reference design</t>
+          <t xml:space="preserve">vanadium electrolyte conditioning</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
@@ -4682,7 +4682,7 @@
     <row r="182" spans="1:13" ns3:dyDescent="0.2">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer gasket compound production, FKM, FE5540 type</t>
         </is>
       </c>
       <c r="B182" s="3">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer gasket compound, FKM, FE5540 type</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>market for used redox-flow battery, Vanadium, reference design</t>
+          <t xml:space="preserve">market for used redox-flow battery, vanadium</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>used redox-flow battery, Vanadium, reference design</t>
+          <t xml:space="preserve">used redox-flow battery, vanadium</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9567,8 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change. Per kg nominal installed system; includes treatment of one replacement stack over 20 years. No substitution or recovery-credit changes.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for used redox-flow battery, Vanadium, reference design. Former reference product: used redox-flow battery, Vanadium, reference design. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+VRFB reference correction v1 (2026-10-17). Independent reconstruction: Oxkem VOS16 2024 electrolyte; Martin 2020 electrochemical reduction; Weber 2018 hardware and lifetime. Nominal capacity uses paired one-electron V charge at Li 2011's 1.25 V standard potential, an explicit reference assumption, not a measured discharge average. Legacy '8.3 MWh' activity name is an identifier, not the reconstructed capacity. The source archive's unspecified remaining-error warning is unresolved; no archive processes are copied. See data/battery/vanadium_reference_design.json and stationary battery documentation for calculations and coverage gaps. Fixed design at all years, no imposed primary/secondary-share change. Per kg nominal installed system; includes treatment of one replacement stack over 20 years. No substitution or recovery-credit changes.</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9624,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>market for used redox-flow battery, Vanadium, reference design</t>
+          <t xml:space="preserve">market for used redox-flow battery, vanadium</t>
         </is>
       </c>
       <c r="B486">
@@ -9647,7 +9648,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>used redox-flow battery, Vanadium, reference design</t>
+          <t xml:space="preserve">used redox-flow battery, vanadium</t>
         </is>
       </c>
       <c r="H486"/>
@@ -9788,7 +9789,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+          <t xml:space="preserve">PFSA membrane production, vanadium redox-flow battery, EW1100</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9823,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+          <t xml:space="preserve">PFSA membrane, vanadium redox-flow battery, EW1100</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9859,8 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>APPROVED VRFB PFSA CHEMICAL IDENTITIES AND BALANCED SUPPLY, issue99, 2026-10-18. Weber2018 DOI10.1021/acs.est.8b02073 SI TableS2; balanced engineering reference approved inissue90 forfinishedEW1100acidPFSA. This appliesidenticalnetchemistrytotheexistingVRFB150kgmembrane/stack,notanadditionalmembrane layer. Original3.2kghexafluoroethane(C2F6)waslabelledhexafluoropropene(C3F6),and2.36kgSodiumchloratebiospherewaslabelledNaCl. Thesearechemicallydifferentmaterials. ReplaceoriginalunbalancedwholechemicalvectorbyonebalancedfinishedPFSAreferencefromissue90,notjustrenameC2F6whileleavingotherimbalances. EW1100,90%finishedretention,100%netintermediateconversion,10kgwater/kg,39.31MJheat+1kWh/kg aggregateallowances andallindustrialPFAS/purity/solvent/abatementgapsfromissue90apply. Productionoforiginalnafionmembrane remains1kg;retainoriginalfactory4e-10unitand0.87tkmlorry/5.22tkmtrain atwrapperonce. Nootheroriginalheat,rawchemicals,biosphereNaCl/NaOH/CO2orwastesremainonwrapper;newrefownsnetreaction/wastesonce.150kgfinishedmembraneinVRFBstackunchanged. Grossrawchemicalfeed changesbydesign,notbyrenormalizingallinputs. DedicatedproviderwithinexistingVRFBworkbookavoidsunresolvedcrossworkbookforwarddependency;identicalchemistryisnotdoublepurchased. GenericNaF-bearingWWTisnotdemonstratedfluorideabatement;uncertainPFASemissionsnotclaimedzeroindustrialemissions. No changesinvanadiumelectrolyte,hardwarecapacity,lifetimeorprimary-secondaryshares.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: VRFB PFSA membrane, EW1100, balanced chemistry reference. Former reference product: VRFB PFSA membrane, EW1100, balanced chemistry reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED VRFB PFSA CHEMICAL IDENTITIES AND BALANCED SUPPLY, issue99, 2026-10-18. Weber2018 DOI10.1021/acs.est.8b02073 SI TableS2; balanced engineering reference approved inissue90 forfinishedEW1100acidPFSA. This appliesidenticalnetchemistrytotheexistingVRFB150kgmembrane/stack,notanadditionalmembrane layer. Original3.2kghexafluoroethane(C2F6)waslabelledhexafluoropropene(C3F6),and2.36kgSodiumchloratebiospherewaslabelledNaCl. Thesearechemicallydifferentmaterials. ReplaceoriginalunbalancedwholechemicalvectorbyonebalancedfinishedPFSAreferencefromissue90,notjustrenameC2F6whileleavingotherimbalances. EW1100,90%finishedretention,100%netintermediateconversion,10kgwater/kg,39.31MJheat+1kWh/kg aggregateallowances andallindustrialPFAS/purity/solvent/abatementgapsfromissue90apply. Productionoforiginalnafionmembrane remains1kg;retainoriginalfactory4e-10unitand0.87tkmlorry/5.22tkmtrain atwrapperonce. Nootheroriginalheat,rawchemicals,biosphereNaCl/NaOH/CO2orwastesremainonwrapper;newrefownsnetreaction/wastesonce.150kgfinishedmembraneinVRFBstackunchanged. Grossrawchemicalfeed changesbydesign,notbyrenormalizingallinputs. DedicatedproviderwithinexistingVRFBworkbookavoidsunresolvedcrossworkbookforwarddependency;identicalchemistryisnotdoublepurchased. GenericNaF-bearingWWTisnotdemonstratedfluorideabatement;uncertainPFASemissionsnotclaimedzeroindustrialemissions. No changesinvanadiumelectrolyte,hardwarecapacity,lifetimeorprimary-secondaryshares.</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9921,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+          <t xml:space="preserve">PFSA membrane production, vanadium redox-flow battery, EW1100</t>
         </is>
       </c>
       <c r="B502">
@@ -9942,12 +9944,12 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+          <t xml:space="preserve">PFSA membrane, vanadium redox-flow battery, EW1100</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>VRFB PFSA membrane, EW1100, balanced chemistry reference</t>
+          <t xml:space="preserve">PFSA membrane, vanadium redox-flow battery, EW1100</t>
         </is>
       </c>
     </row>
@@ -10374,7 +10376,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+          <t xml:space="preserve">vinylidene fluoride production, chlorination and fluorination</t>
         </is>
       </c>
     </row>
@@ -10408,7 +10410,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10446,8 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: VDF monomer, chlorination-fluorination net engineering reference. Former reference product: VDF monomer, chlorination-fluorination net engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
 Replace the chemically incompatible 0.33kg each of hexafluoroethane gas, TFE monomer and polyvinylfluoride perkg gasket. Adopt the published FE5540-type terpolymer reference at monomer massfractions {'VDF': 0.5926861629718567, 'HFP': 0.29622824511137696, 'TFE': 0.11108559191676634}, converted from molar fractions, rather than equal mass thirds. Finished compounded gasket formulation uses100/139 commercial-grade FKM,30/139 carbonblack,6/139 hydratedlime and3/139 MgO by mass. The source recipe demonstrates a cured compound, not a measured VRFB gasket. Retain installed gasket mass and all consumer allocations, including organic/hybrid flow-battery consumers of this shared provider.
 The commercial grade contains unspecified incorporated cure ingredients. Partition99% to modeled terpolymer and1% to a generic organic-chemical cure-package allowance. This1% is an explicit engineering coverage proxy, not published FE5540 assay, not a claim of metal-free catalyst/accelerator composition, and not bisphenol-A substituted for bisphenol-AF. Sensitivity0-3% incorporated package required. Do not add an extra full resin mass. FKM polymerization1kWh+6MJ/kg and10kg processwater/kg are engineering allowances;95% polymer retention assigns5% handling/unrecovered monomers to captured hazardous waste. Actual initiator/emulsifier/catalyst doses, fluorinated fugitives, purification and end groups remain gaps;100% capture is an inventory reference, not measured control efficiency.
 Because VDF is absent from older supported ecoinvent versions, define one common net route from vinylchloride through111TCA/142b toVDF: VC+Cl2+2HF -&gt;VDF+3HCl. Internal hydrochlorination HCl cancels from net feed. Scrub net HCl with3NaOH -&gt;3NaCl+3H2O. Reference feedkg perkg finishedVDF={'vinyl_chloride': 1.0273360213347598, 'chlorine': 1.165484573614863, 'HF': 0.6577476519039802, 'NaOH': 1.9724520842146482, 'water': 20.0}; rejectVDF=0.05263157894736836kg; brine=23.770388752120883kg at1100kg/m3. Assume95% finishedVDF retention after complete net conversion/recycle, not95% one-pass selectivity; generic brine WWT is not demonstrated salt removal. Use2kWh+10MJ/kgVDF and1gAlCl3/kgVDF catalyst-makeup allowance with equal collected spentcatalyst mass; these are engineering utilities/makeup, not patent measured plant inventory. Catalytic fluorination chemistry and commercial purification may require additional reagents; no certified commodity inventory is claimed. Chlorinated-gas fugitives are unresolved, not proven zero. Sensitivity catalyst0.1-10g/kg andutilities0.5-3x.
@@ -10511,7 +10514,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+          <t xml:space="preserve">vinylidene fluoride production, chlorination and fluorination</t>
         </is>
       </c>
       <c r="B526">
@@ -10534,12 +10537,12 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
         </is>
       </c>
     </row>
@@ -10901,7 +10904,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+          <t xml:space="preserve">hexafluoropropylene production, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
     </row>
@@ -10935,7 +10938,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
     </row>
@@ -10971,7 +10974,8 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: HFP monomer, TFE pyrolysis net engineering reference. Former reference product: HFP monomer, TFE pyrolysis net engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
 Replace the chemically incompatible 0.33kg each of hexafluoroethane gas, TFE monomer and polyvinylfluoride perkg gasket. Adopt the published FE5540-type terpolymer reference at monomer massfractions {'VDF': 0.5926861629718567, 'HFP': 0.29622824511137696, 'TFE': 0.11108559191676634}, converted from molar fractions, rather than equal mass thirds. Finished compounded gasket formulation uses100/139 commercial-grade FKM,30/139 carbonblack,6/139 hydratedlime and3/139 MgO by mass. The source recipe demonstrates a cured compound, not a measured VRFB gasket. Retain installed gasket mass and all consumer allocations, including organic/hybrid flow-battery consumers of this shared provider.
 The commercial grade contains unspecified incorporated cure ingredients. Partition99% to modeled terpolymer and1% to a generic organic-chemical cure-package allowance. This1% is an explicit engineering coverage proxy, not published FE5540 assay, not a claim of metal-free catalyst/accelerator composition, and not bisphenol-A substituted for bisphenol-AF. Sensitivity0-3% incorporated package required. Do not add an extra full resin mass. FKM polymerization1kWh+6MJ/kg and10kg processwater/kg are engineering allowances;95% polymer retention assigns5% handling/unrecovered monomers to captured hazardous waste. Actual initiator/emulsifier/catalyst doses, fluorinated fugitives, purification and end groups remain gaps;100% capture is an inventory reference, not measured control efficiency.
 Because VDF is absent from older supported ecoinvent versions, define one common net route from vinylchloride through111TCA/142b toVDF: VC+Cl2+2HF -&gt;VDF+3HCl. Internal hydrochlorination HCl cancels from net feed. Scrub net HCl with3NaOH -&gt;3NaCl+3H2O. Reference feedkg perkg finishedVDF={'vinyl_chloride': 1.0273360213347598, 'chlorine': 1.165484573614863, 'HF': 0.6577476519039802, 'NaOH': 1.9724520842146482, 'water': 20.0}; rejectVDF=0.05263157894736836kg; brine=23.770388752120883kg at1100kg/m3. Assume95% finishedVDF retention after complete net conversion/recycle, not95% one-pass selectivity; generic brine WWT is not demonstrated salt removal. Use2kWh+10MJ/kgVDF and1gAlCl3/kgVDF catalyst-makeup allowance with equal collected spentcatalyst mass; these are engineering utilities/makeup, not patent measured plant inventory. Catalytic fluorination chemistry and commercial purification may require additional reagents; no certified commodity inventory is claimed. Chlorinated-gas fugitives are unresolved, not proven zero. Sensitivity catalyst0.1-10g/kg andutilities0.5-3x.
@@ -11038,7 +11042,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+          <t xml:space="preserve">hexafluoropropylene production, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
       <c r="B548">
@@ -11061,12 +11065,12 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11222,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer production, FKM terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11256,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
     </row>
@@ -11288,7 +11292,8 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: FKM terpolymer, 75-16-9 molar engineering reference. Former reference product: FKM terpolymer, 75-16-9 molar engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
 Replace the chemically incompatible 0.33kg each of hexafluoroethane gas, TFE monomer and polyvinylfluoride perkg gasket. Adopt the published FE5540-type terpolymer reference at monomer massfractions {'VDF': 0.5926861629718567, 'HFP': 0.29622824511137696, 'TFE': 0.11108559191676634}, converted from molar fractions, rather than equal mass thirds. Finished compounded gasket formulation uses100/139 commercial-grade FKM,30/139 carbonblack,6/139 hydratedlime and3/139 MgO by mass. The source recipe demonstrates a cured compound, not a measured VRFB gasket. Retain installed gasket mass and all consumer allocations, including organic/hybrid flow-battery consumers of this shared provider.
 The commercial grade contains unspecified incorporated cure ingredients. Partition99% to modeled terpolymer and1% to a generic organic-chemical cure-package allowance. This1% is an explicit engineering coverage proxy, not published FE5540 assay, not a claim of metal-free catalyst/accelerator composition, and not bisphenol-A substituted for bisphenol-AF. Sensitivity0-3% incorporated package required. Do not add an extra full resin mass. FKM polymerization1kWh+6MJ/kg and10kg processwater/kg are engineering allowances;95% polymer retention assigns5% handling/unrecovered monomers to captured hazardous waste. Actual initiator/emulsifier/catalyst doses, fluorinated fugitives, purification and end groups remain gaps;100% capture is an inventory reference, not measured control efficiency.
 Because VDF is absent from older supported ecoinvent versions, define one common net route from vinylchloride through111TCA/142b toVDF: VC+Cl2+2HF -&gt;VDF+3HCl. Internal hydrochlorination HCl cancels from net feed. Scrub net HCl with3NaOH -&gt;3NaCl+3H2O. Reference feedkg perkg finishedVDF={'vinyl_chloride': 1.0273360213347598, 'chlorine': 1.165484573614863, 'HF': 0.6577476519039802, 'NaOH': 1.9724520842146482, 'water': 20.0}; rejectVDF=0.05263157894736836kg; brine=23.770388752120883kg at1100kg/m3. Assume95% finishedVDF retention after complete net conversion/recycle, not95% one-pass selectivity; generic brine WWT is not demonstrated salt removal. Use2kWh+10MJ/kgVDF and1gAlCl3/kgVDF catalyst-makeup allowance with equal collected spentcatalyst mass; these are engineering utilities/makeup, not patent measured plant inventory. Catalytic fluorination chemistry and commercial purification may require additional reagents; no certified commodity inventory is claimed. Chlorinated-gas fugitives are unresolved, not proven zero. Sensitivity catalyst0.1-10g/kg andutilities0.5-3x.
@@ -11355,7 +11360,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer production, FKM terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
       <c r="B564">
@@ -11378,19 +11383,19 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+          <t xml:space="preserve">vinylidene fluoride production, chlorination and fluorination</t>
         </is>
       </c>
       <c r="B565">
@@ -11413,19 +11418,19 @@
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>VDF monomer, chlorination-fluorination net engineering reference</t>
+          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+          <t xml:space="preserve">hexafluoropropylene production, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
       <c r="B566">
@@ -11448,12 +11453,12 @@
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>HFP monomer, TFE pyrolysis net engineering reference</t>
+          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11680,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer gasket compound production, FKM, FE5540 type</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11714,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer gasket compound, FKM, FE5540 type</t>
         </is>
       </c>
     </row>
@@ -11745,7 +11750,8 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: finished FKM gasket compound, FE5540-type engineering reference. Former reference product: finished FKM gasket compound, FE5540-type engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
 Replace the chemically incompatible 0.33kg each of hexafluoroethane gas, TFE monomer and polyvinylfluoride perkg gasket. Adopt the published FE5540-type terpolymer reference at monomer massfractions {'VDF': 0.5926861629718567, 'HFP': 0.29622824511137696, 'TFE': 0.11108559191676634}, converted from molar fractions, rather than equal mass thirds. Finished compounded gasket formulation uses100/139 commercial-grade FKM,30/139 carbonblack,6/139 hydratedlime and3/139 MgO by mass. The source recipe demonstrates a cured compound, not a measured VRFB gasket. Retain installed gasket mass and all consumer allocations, including organic/hybrid flow-battery consumers of this shared provider.
 The commercial grade contains unspecified incorporated cure ingredients. Partition99% to modeled terpolymer and1% to a generic organic-chemical cure-package allowance. This1% is an explicit engineering coverage proxy, not published FE5540 assay, not a claim of metal-free catalyst/accelerator composition, and not bisphenol-A substituted for bisphenol-AF. Sensitivity0-3% incorporated package required. Do not add an extra full resin mass. FKM polymerization1kWh+6MJ/kg and10kg processwater/kg are engineering allowances;95% polymer retention assigns5% handling/unrecovered monomers to captured hazardous waste. Actual initiator/emulsifier/catalyst doses, fluorinated fugitives, purification and end groups remain gaps;100% capture is an inventory reference, not measured control efficiency.
 Because VDF is absent from older supported ecoinvent versions, define one common net route from vinylchloride through111TCA/142b toVDF: VC+Cl2+2HF -&gt;VDF+3HCl. Internal hydrochlorination HCl cancels from net feed. Scrub net HCl with3NaOH -&gt;3NaCl+3H2O. Reference feedkg perkg finishedVDF={'vinyl_chloride': 1.0273360213347598, 'chlorine': 1.165484573614863, 'HF': 0.6577476519039802, 'NaOH': 1.9724520842146482, 'water': 20.0}; rejectVDF=0.05263157894736836kg; brine=23.770388752120883kg at1100kg/m3. Assume95% finishedVDF retention after complete net conversion/recycle, not95% one-pass selectivity; generic brine WWT is not demonstrated salt removal. Use2kWh+10MJ/kgVDF and1gAlCl3/kgVDF catalyst-makeup allowance with equal collected spentcatalyst mass; these are engineering utilities/makeup, not patent measured plant inventory. Catalytic fluorination chemistry and commercial purification may require additional reagents; no certified commodity inventory is claimed. Chlorinated-gas fugitives are unresolved, not proven zero. Sensitivity catalyst0.1-10g/kg andutilities0.5-3x.
@@ -11812,7 +11818,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer gasket compound production, FKM, FE5540 type</t>
         </is>
       </c>
       <c r="B584">
@@ -11835,19 +11841,19 @@
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer gasket compound, FKM, FE5540 type</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>finished FKM gasket compound, FE5540-type engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer gasket compound, FKM, FE5540 type</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer production, FKM terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
       <c r="B585">
@@ -11870,12 +11876,12 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
         <is>
-          <t>FKM terpolymer, 75-16-9 molar engineering reference</t>
+          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F109" t="s">
@@ -3464,7 +3464,8 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>Conditioning service per kg final electrolyte: make-up water, V reduction electricity and O2 output. Materials remain separate.</t>
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Conditioning of one kilogram of final electrolyte solution. Unit field: kilogram. Former reference: 1 unit = 1 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Conditioning service per kg final electrolyte: make-up water, V reduction electricity and O2 output. Materials remain separate.</t>
         </is>
       </c>
       <c r="I109" s="3"/>

--- a/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-vanadium-redox-flow.xlsx
@@ -1600,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2F1C5B3A-29A3-3D4D-87B5-E2283E6AD55F}">
-  <dimension ref="A1:P591"/>
+  <dimension ref="A1:P597"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="63" customWidth="1"/>
@@ -1765,9 +1765,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" ns3:dyDescent="0.2">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PFSA membrane production, vanadium redox-flow battery, EW1100</t>
+      <c r="A14" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">perfluorosulfonic acid membrane production, vanadium redox-flow battery, ew1100</t>
         </is>
       </c>
       <c r="B14" s="5">
@@ -4681,9 +4681,9 @@
       </c>
     </row>
     <row r="182" spans="1:13" ns3:dyDescent="0.2">
-      <c r="A182" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer gasket compound production, FKM, FE5540 type</t>
+      <c r="A182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">fluoroelastomer gasket compound production, fkm, fe5540 type</t>
         </is>
       </c>
       <c r="B182" s="3">
@@ -9576,96 +9576,77 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">source</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oxkem VOS16 (2024), Martin (2020) and Weber (2018), reconstructed reference documented in premise/data/battery/vanadium_reference_design.json and the activity comment; unvalidated industrial conditioning and treatment proxies remain explicit limitations.
+Explicit reference links (source or inherited supplier evidence; the engineering adaptation is documented in the activity comment): https://zenodo.org/records/10589869 ; https://www.oxkem.com/wp-content/uploads/2025/04/Vanadium-Electrolyte-TDS-1.6mol.L.pdf ; https://d-nb.info/1260641937/34 ; https://www.pnnl.gov/sites/default/files/media/file/at/publications/333_926201145351.pdf</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F485" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G485" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H485" t="inlineStr">
-        <is>
-          <t>comment</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for used redox-flow battery, vanadium</t>
-        </is>
-      </c>
-      <c r="B486">
-        <v>-1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="E486"/>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t xml:space="preserve">used redox-flow battery, vanadium</t>
-        </is>
-      </c>
-      <c r="H486"/>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>treatment of stack, for VRFB system</t>
+          <t xml:space="preserve">market for used redox-flow battery, vanadium</t>
         </is>
       </c>
       <c r="B487">
-        <v>-0.06260978277855915</v>
+        <v>-1</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -9676,12 +9657,12 @@
       <c r="E487"/>
       <c r="F487" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>used stack, for VRFB system</t>
+          <t xml:space="preserve">used redox-flow battery, vanadium</t>
         </is>
       </c>
       <c r="H487"/>
@@ -9689,11 +9670,11 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>treatment of electrolyte tank, for VRFB system</t>
+          <t>treatment of stack, for VRFB system</t>
         </is>
       </c>
       <c r="B488">
-        <v>-0.10185654008438819</v>
+        <v>-0.06260978277855915</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
@@ -9713,7 +9694,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>used electrolyte tank, for VRFB system</t>
+          <t>used stack, for VRFB system</t>
         </is>
       </c>
       <c r="H488"/>
@@ -9721,11 +9702,11 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>treatment of electrolyte solution, for VRFB system</t>
+          <t>treatment of electrolyte tank, for VRFB system</t>
         </is>
       </c>
       <c r="B489">
-        <v>-0.8508204406938584</v>
+        <v>-0.10185654008438819</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
@@ -9745,7 +9726,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>used electrolyte solution, for VRFB system</t>
+          <t>used electrolyte tank, for VRFB system</t>
         </is>
       </c>
       <c r="H489"/>
@@ -9753,11 +9734,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>treatment of periphericals, for VRFB system</t>
+          <t>treatment of electrolyte solution, for VRFB system</t>
         </is>
       </c>
       <c r="B490">
-        <v>-0.016018127832473823</v>
+        <v>-0.8508204406938584</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
@@ -9777,230 +9758,204 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
+          <t>used electrolyte solution, for VRFB system</t>
+        </is>
+      </c>
+      <c r="H490"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>treatment of periphericals, for VRFB system</t>
+        </is>
+      </c>
+      <c r="B491">
+        <v>-0.016018127832473823</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E491"/>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
           <t>used periphericals, for VRFB system</t>
         </is>
       </c>
-      <c r="H490"/>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PFSA membrane production, vanadium redox-flow battery, EW1100</t>
-        </is>
-      </c>
+      <c r="H491"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t xml:space="preserve">perfluorosulfonic acid membrane production, vanadium redox-flow battery, ew1100</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B495">
-        <v>1</v>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PFSA membrane, vanadium redox-flow battery, EW1100</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B496">
+        <v>1</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t xml:space="preserve">PFSA membrane, vanadium redox-flow battery, EW1100</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Weber2018 DOI10.1021/acs.est.8b02073 SI TableS2; balanced engineering reference approved inissue90 forfinishedEW1100acidPFSA. This appliesidenticalnetchemistrytotheexistingVRFB150kgmembrane/stack,notanadditionalmembrane layer.</t>
+          <t>kilogram</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Weber2018 DOI10.1021/acs.est.8b02073 SI TableS2; balanced engineering reference approved inissue90 forfinishedEW1100acidPFSA. This appliesidenticalnetchemistrytotheexistingVRFB150kgmembrane/stack,notanadditionalmembrane layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B499" t="inlineStr">
+      <c r="B500" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: VRFB PFSA membrane, EW1100, balanced chemistry reference. Former reference product: VRFB PFSA membrane, EW1100, balanced chemistry reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED VRFB PFSA CHEMICAL IDENTITIES AND BALANCED SUPPLY, issue99, 2026-10-18. Weber2018 DOI10.1021/acs.est.8b02073 SI TableS2; balanced engineering reference approved inissue90 forfinishedEW1100acidPFSA. This appliesidenticalnetchemistrytotheexistingVRFB150kgmembrane/stack,notanadditionalmembrane layer. Original3.2kghexafluoroethane(C2F6)waslabelledhexafluoropropene(C3F6),and2.36kgSodiumchloratebiospherewaslabelledNaCl. Thesearechemicallydifferentmaterials. ReplaceoriginalunbalancedwholechemicalvectorbyonebalancedfinishedPFSAreferencefromissue90,notjustrenameC2F6whileleavingotherimbalances. EW1100,90%finishedretention,100%netintermediateconversion,10kgwater/kg,39.31MJheat+1kWh/kg aggregateallowances andallindustrialPFAS/purity/solvent/abatementgapsfromissue90apply. Productionoforiginalnafionmembrane remains1kg;retainoriginalfactory4e-10unitand0.87tkmlorry/5.22tkmtrain atwrapperonce. Nootheroriginalheat,rawchemicals,biosphereNaCl/NaOH/CO2orwastesremainonwrapper;newrefownsnetreaction/wastesonce.150kgfinishedmembraneinVRFBstackunchanged. Grossrawchemicalfeed changesbydesign,notbyrenormalizingallinputs. DedicatedproviderwithinexistingVRFBworkbookavoidsunresolvedcrossworkbookforwarddependency;identicalchemistryisnotdoublepurchased. GenericNaF-bearingWWTisnotdemonstratedfluorideabatement;uncertainPFASemissionsnotclaimedzeroindustrialemissions. No changesinvanadiumelectrolyte,hardwarecapacity,lifetimeorprimary-secondaryshares.</t>
         </is>
       </c>
     </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>name</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E501" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G501" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H501" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I501" t="inlineStr">
-        <is>
-          <t>product</t>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t xml:space="preserve">PFSA membrane production, vanadium redox-flow battery, EW1100</t>
-        </is>
-      </c>
-      <c r="B502">
-        <v>1</v>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F502" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G502" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PFSA membrane, vanadium redox-flow battery, EW1100</t>
-        </is>
-      </c>
-      <c r="I502" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PFSA membrane, vanadium redox-flow battery, EW1100</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>market for tetrafluoroethylene</t>
-        </is>
-      </c>
-      <c r="B503">
-        <v>1.0666093025141414</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>tetrafluoroethylene</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>tetrafluoroethylene</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>market for sulfur trioxide</t>
+          <t xml:space="preserve">perfluorosulfonic acid membrane production, vanadium redox-flow battery, ew1100</t>
         </is>
       </c>
       <c r="B504">
-        <v>0.08086565656565657</v>
+        <v>1</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -10010,32 +9965,32 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>sulfur trioxide</t>
+          <t xml:space="preserve">PFSA membrane, vanadium redox-flow battery, EW1100</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>sulfur trioxide</t>
+          <t xml:space="preserve">PFSA membrane, vanadium redox-flow battery, EW1100</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>market for sodium hypochlorite, without water, in 15% solution state</t>
+          <t>market for tetrafluoroethylene</t>
         </is>
       </c>
       <c r="B505">
-        <v>0.15038135208080808</v>
+        <v>1.0666093025141414</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -10050,27 +10005,27 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>sodium hypochlorite, without water, in 15% solution state</t>
+          <t>tetrafluoroethylene</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>sodium hypochlorite, without water, in 15% solution state</t>
+          <t>tetrafluoroethylene</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>market for soda ash, dense</t>
+          <t>market for sulfur trioxide</t>
         </is>
       </c>
       <c r="B506">
-        <v>0.10705811975757576</v>
+        <v>0.08086565656565657</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -10085,27 +10040,27 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>soda ash, dense</t>
+          <t>sulfur trioxide</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>soda ash, dense</t>
+          <t>sulfur trioxide</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>market for sodium hydroxide, without water, in 50% solution state</t>
+          <t>market for sodium hypochlorite, without water, in 15% solution state</t>
         </is>
       </c>
       <c r="B507">
-        <v>0.0808015541010101</v>
+        <v>0.15038135208080808</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -10120,27 +10075,27 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>sodium hydroxide, without water, in 50% solution state</t>
+          <t>sodium hypochlorite, without water, in 15% solution state</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>sodium hydroxide, without water, in 50% solution state</t>
+          <t>sodium hypochlorite, without water, in 15% solution state</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>market for hydrochloric acid, without water, in 30% solution state</t>
+          <t>market for soda ash, dense</t>
         </is>
       </c>
       <c r="B508">
-        <v>0.03682626262626263</v>
+        <v>0.10705811975757576</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -10155,27 +10110,27 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>hydrochloric acid, without water, in 30% solution state</t>
+          <t>soda ash, dense</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>hydrochloric acid, without water, in 30% solution state</t>
+          <t>soda ash, dense</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>market for tap water</t>
+          <t>market for sodium hydroxide, without water, in 50% solution state</t>
         </is>
       </c>
       <c r="B509">
-        <v>10</v>
+        <v>0.0808015541010101</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -10190,23 +10145,23 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>tap water</t>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>tap water</t>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>market for wastewater, average</t>
+          <t>market for hydrochloric acid, without water, in 30% solution state</t>
         </is>
       </c>
       <c r="B510">
-        <v>-0.010322524065827272</v>
+        <v>0.03682626262626263</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
@@ -10215,7 +10170,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>cubic meter</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
@@ -10225,23 +10180,23 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>treatment of waste plastic, mixture, municipal incineration</t>
+          <t>market for tap water</t>
         </is>
       </c>
       <c r="B511">
-        <v>-0.11111111111111116</v>
+        <v>10</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
@@ -10260,23 +10215,23 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>waste plastic, mixture</t>
+          <t>tap water</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>waste plastic, mixture</t>
+          <t>tap water</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>market for heat, district or industrial, natural gas</t>
+          <t>market for wastewater, average</t>
         </is>
       </c>
       <c r="B512">
-        <v>39.31</v>
+        <v>-0.010322524065827272</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
@@ -10285,7 +10240,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>megajoule</t>
+          <t>cubic meter</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -10295,32 +10250,32 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>wastewater, average</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>wastewater, average</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>treatment of waste plastic, mixture, municipal incineration</t>
         </is>
       </c>
       <c r="B513">
-        <v>1</v>
+        <v>-0.11111111111111116</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RoW</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -10330,122 +10285,192 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>waste plastic, mixture</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>waste plastic, mixture</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B514">
+        <v>39.31</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B515">
+        <v>1</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
           <t>Carbon dioxide, fossil</t>
         </is>
       </c>
-      <c r="B514">
+      <c r="B516">
         <v>0.08890707070707071</v>
       </c>
-      <c r="D514" t="inlineStr">
+      <c r="D516" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="E514" t="inlineStr">
+      <c r="E516" t="inlineStr">
         <is>
           <t>air::non-urban air or from high stacks</t>
         </is>
       </c>
-      <c r="F514" t="inlineStr">
+      <c r="F516" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>
       </c>
-      <c r="H514" t="inlineStr">
+      <c r="H516" t="inlineStr">
         <is>
           <t/>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vinylidene fluoride production, chlorination and fluorination</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B519">
-        <v>1</v>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vinylidene fluoride production, chlorination and fluorination</t>
+        </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B521">
+        <v>1</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
+          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B523" t="inlineStr">
+      <c r="B525" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: VDF monomer, chlorination-fluorination net engineering reference. Former reference product: VDF monomer, chlorination-fluorination net engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
@@ -10458,177 +10483,84 @@
         </is>
       </c>
     </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E525" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F525" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G525" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I525" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t xml:space="preserve">vinylidene fluoride production, chlorination and fluorination</t>
-        </is>
-      </c>
-      <c r="B526">
-        <v>1</v>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F526" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G526" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
-        </is>
-      </c>
-      <c r="I526" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>market for vinyl chloride</t>
-        </is>
-      </c>
-      <c r="B527">
-        <v>1.0273360213347598</v>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F527" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>vinyl chloride</t>
-        </is>
-      </c>
-      <c r="I527" t="inlineStr">
-        <is>
-          <t>vinyl chloride</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>market for chlorine, liquid</t>
-        </is>
-      </c>
-      <c r="B528">
-        <v>1.165484573614863</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>chlorine, liquid</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>chlorine, liquid</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>market for hydrogen fluoride</t>
+          <t xml:space="preserve">vinylidene fluoride production, chlorination and fluorination</t>
         </is>
       </c>
       <c r="B529">
-        <v>0.6577476519039802</v>
+        <v>1</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -10638,32 +10570,32 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>hydrogen fluoride</t>
+          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>hydrogen fluoride</t>
+          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>market for sodium hydroxide, without water, in 50% solution state</t>
+          <t>market for vinyl chloride</t>
         </is>
       </c>
       <c r="B530">
-        <v>1.9724520842146482</v>
+        <v>1.0273360213347598</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -10678,27 +10610,27 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>sodium hydroxide, without water, in 50% solution state</t>
+          <t>vinyl chloride</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>sodium hydroxide, without water, in 50% solution state</t>
+          <t>vinyl chloride</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>market for tap water</t>
+          <t>market for chlorine, liquid</t>
         </is>
       </c>
       <c r="B531">
-        <v>18.02754791578535</v>
+        <v>1.165484573614863</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -10713,27 +10645,27 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>tap water</t>
+          <t>chlorine, liquid</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>tap water</t>
+          <t>chlorine, liquid</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>market for aluminium chloride</t>
+          <t>market for hydrogen fluoride</t>
         </is>
       </c>
       <c r="B532">
-        <v>0.001</v>
+        <v>0.6577476519039802</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -10748,27 +10680,27 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>aluminium chloride</t>
+          <t>hydrogen fluoride</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>aluminium chloride</t>
+          <t>hydrogen fluoride</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>market for hazardous waste, for incineration</t>
+          <t>market for sodium hydroxide, without water, in 50% solution state</t>
         </is>
       </c>
       <c r="B533">
-        <v>-0.053631578947368364</v>
+        <v>1.9724520842146482</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -10783,23 +10715,23 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>hazardous waste, for incineration</t>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>hazardous waste, for incineration</t>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>market for wastewater, average</t>
+          <t>market for tap water</t>
         </is>
       </c>
       <c r="B534">
-        <v>-0.021609444320109895</v>
+        <v>18.02754791578535</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
@@ -10808,7 +10740,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>cubic meter</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
@@ -10818,23 +10750,23 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t>tap water</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t>tap water</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>market for aluminium chloride</t>
         </is>
       </c>
       <c r="B535">
-        <v>2</v>
+        <v>0.001</v>
       </c>
       <c r="C535" t="inlineStr">
         <is>
@@ -10843,7 +10775,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
@@ -10853,23 +10785,23 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>aluminium chloride</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>aluminium chloride</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>market for heat, district or industrial, natural gas</t>
+          <t>market for hazardous waste, for incineration</t>
         </is>
       </c>
       <c r="B536">
-        <v>10</v>
+        <v>-0.053631578947368364</v>
       </c>
       <c r="C536" t="inlineStr">
         <is>
@@ -10878,7 +10810,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>megajoule</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
@@ -10888,92 +10820,197 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>hazardous waste, for incineration</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B537">
+        <v>-0.021609444320109895</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B538">
+        <v>2</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hexafluoropropylene production, tetrafluoroethylene pyrolysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B541">
-        <v>1</v>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B539">
+        <v>10</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
+          <t xml:space="preserve">hexafluoropropylene production, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B544">
+        <v>1</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B545" t="inlineStr">
+      <c r="B548" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: HFP monomer, TFE pyrolysis net engineering reference. Former reference product: HFP monomer, TFE pyrolysis net engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
@@ -10986,312 +11023,324 @@
         </is>
       </c>
     </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E547" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F547" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G547" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H547" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I547" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hexafluoropropylene production, tetrafluoroethylene pyrolysis</t>
-        </is>
-      </c>
-      <c r="B548">
-        <v>1</v>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F548" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G548" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
-        </is>
-      </c>
-      <c r="I548" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
-        </is>
-      </c>
-    </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>market for tetrafluoroethylene</t>
-        </is>
-      </c>
-      <c r="B549">
-        <v>1.0526315789473684</v>
-      </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F549" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G549" t="inlineStr">
-        <is>
-          <t>tetrafluoroethylene</t>
-        </is>
-      </c>
-      <c r="I549" t="inlineStr">
-        <is>
-          <t>tetrafluoroethylene</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>market for hazardous waste, for incineration</t>
-        </is>
-      </c>
-      <c r="B550">
-        <v>-0.05263157894736836</v>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>RoW</t>
-        </is>
-      </c>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G550" t="inlineStr">
-        <is>
-          <t>hazardous waste, for incineration</t>
-        </is>
-      </c>
-      <c r="I550" t="inlineStr">
-        <is>
-          <t>hazardous waste, for incineration</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B551">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>market for heat, district or industrial, natural gas</t>
+          <t xml:space="preserve">hexafluoropropylene production, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
       <c r="B552">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>market for tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="B553">
+        <v>1.0526315789473684</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B554">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
           <t>RoW</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>megajoule</t>
-        </is>
-      </c>
-      <c r="F552" t="inlineStr">
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G552" t="inlineStr">
-        <is>
-          <t>heat, district or industrial, natural gas</t>
-        </is>
-      </c>
-      <c r="I552" t="inlineStr">
-        <is>
-          <t>heat, district or industrial, natural gas</t>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer production, FKM terpolymer, 75/16/9 molar composition</t>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B555">
+        <v>1</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B557">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B556">
+        <v>6</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t xml:space="preserve">fluoroelastomer production, fkm terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B561">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B565" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: FKM terpolymer, 75-16-9 molar engineering reference. Former reference product: FKM terpolymer, 75-16-9 molar engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
@@ -11304,247 +11353,84 @@
         </is>
       </c>
     </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E563" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F563" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G563" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H563" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I563" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer production, FKM terpolymer, 75/16/9 molar composition</t>
-        </is>
-      </c>
-      <c r="B564">
-        <v>1</v>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D564" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F564" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
-        </is>
-      </c>
-      <c r="I564" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vinylidene fluoride production, chlorination and fluorination</t>
-        </is>
-      </c>
-      <c r="B565">
-        <v>0.6238801715493228</v>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F565" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G565" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
-        </is>
-      </c>
-      <c r="I565" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
-        </is>
-      </c>
-    </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t xml:space="preserve">hexafluoropropylene production, tetrafluoroethylene pyrolysis</t>
-        </is>
-      </c>
-      <c r="B566">
-        <v>0.3118192053803968</v>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D566" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F566" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G566" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
-        </is>
-      </c>
-      <c r="I566" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>market for tetrafluoroethylene</t>
-        </is>
-      </c>
-      <c r="B567">
-        <v>0.11693220201764878</v>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F567" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G567" t="inlineStr">
-        <is>
-          <t>tetrafluoroethylene</t>
-        </is>
-      </c>
-      <c r="I567" t="inlineStr">
-        <is>
-          <t>tetrafluoroethylene</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>market for hazardous waste, for incineration</t>
-        </is>
-      </c>
-      <c r="B568">
-        <v>-0.05263157894736836</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>hazardous waste, for incineration</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>hazardous waste, for incineration</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>market for water, deionised</t>
+          <t xml:space="preserve">fluoroelastomer production, fkm terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
       <c r="B569">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -11554,37 +11440,37 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>water, deionised</t>
+          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>water, deionised</t>
+          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>market for wastewater, average</t>
+          <t xml:space="preserve">vinylidene fluoride production, chlorination and fluorination</t>
         </is>
       </c>
       <c r="B570">
-        <v>-0.01</v>
+        <v>0.6238801715493228</v>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>cubic meter</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
@@ -11594,23 +11480,23 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t xml:space="preserve">vinylidene fluoride, chlorination and fluorination</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t xml:space="preserve">hexafluoropropylene production, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
       <c r="B571">
-        <v>1</v>
+        <v>0.3118192053803968</v>
       </c>
       <c r="C571" t="inlineStr">
         <is>
@@ -11619,7 +11505,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
@@ -11629,127 +11515,302 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t xml:space="preserve">hexafluoropropylene, tetrafluoroethylene pyrolysis</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>market for heat, district or industrial, natural gas</t>
+          <t>market for tetrafluoroethylene</t>
         </is>
       </c>
       <c r="B572">
-        <v>6</v>
+        <v>0.11693220201764878</v>
       </c>
       <c r="C572" t="inlineStr">
         <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>tetrafluoroethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B573">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
           <t>RoW</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>megajoule</t>
-        </is>
-      </c>
-      <c r="F572" t="inlineStr">
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G572" t="inlineStr">
-        <is>
-          <t>heat, district or industrial, natural gas</t>
-        </is>
-      </c>
-      <c r="I572" t="inlineStr">
-        <is>
-          <t>heat, district or industrial, natural gas</t>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B574">
+        <v>10</v>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer gasket compound production, FKM, FE5540 type</t>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B575">
+        <v>-0.01</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B576" t="inlineStr">
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B576">
+        <v>1</v>
+      </c>
+      <c r="C576" t="inlineStr">
         <is>
           <t>GLO</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t>market for heat, district or industrial, natural gas</t>
         </is>
       </c>
       <c r="B577">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer gasket compound, FKM, FE5540 type</t>
-        </is>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>kilogram</t>
+        <v>6</v>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
+          <t xml:space="preserve">fluoroelastomer gasket compound production, fkm, fe5540 type</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B582">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fluoroelastomer gasket compound, FKM, FE5540 type</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: finished FKM gasket compound, FE5540-type engineering reference. Former reference product: finished FKM gasket compound, FE5540-type engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED FINISHED FKM GASKET ENGINEERING REFERENCE, issue120, 2026-10-19. Weber2018 SI TableS18 identifies deficient FKM proxies. 3M patent US20130109790A1 Table2: FE5540 75mol%VDF/16%HFP/9%TFE; Table8 ComparativeExample14: 100parts FE5540+30carbonblack+6Ca(OH)2+3MgO, no ionic liquid. https://patents.google.com/patent/US20130109790A1/en . VDF route: US3748243A (VC hydrochlorination/chlorination to111TCA), US8350101B2 (TCA fluorination/142b dehydrochlorination). https://patents.google.com/patent/US3748243A/en ; https://patents.google.com/patent/US8350101B2/en . HFP route: TFE pyrolysis/recycle US2970176A https://patents.google.com/patent/US2970176A/en .
@@ -11762,274 +11823,76 @@
         </is>
       </c>
     </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C583" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F583" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G583" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H583" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I583" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer gasket compound production, FKM, FE5540 type</t>
-        </is>
-      </c>
-      <c r="B584">
-        <v>1</v>
-      </c>
-      <c r="C584" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D584" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F584" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G584" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer gasket compound, FKM, FE5540 type</t>
-        </is>
-      </c>
-      <c r="I584" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer gasket compound, FKM, FE5540 type</t>
-        </is>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer production, FKM terpolymer, 75/16/9 molar composition</t>
-        </is>
-      </c>
-      <c r="B585">
-        <v>0.7122302158273381</v>
-      </c>
-      <c r="C585" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D585" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F585" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G585" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
-        </is>
-      </c>
-      <c r="I585" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>market for chemical, organic</t>
-        </is>
-      </c>
-      <c r="B586">
-        <v>0.007194244604316547</v>
-      </c>
-      <c r="C586" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D586" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F586" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G586" t="inlineStr">
-        <is>
-          <t>chemical, organic</t>
-        </is>
-      </c>
-      <c r="I586" t="inlineStr">
-        <is>
-          <t>chemical, organic</t>
-        </is>
-      </c>
-    </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>market for carbon black</t>
-        </is>
-      </c>
-      <c r="B587">
-        <v>0.2158273381294964</v>
-      </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F587" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G587" t="inlineStr">
-        <is>
-          <t>carbon black</t>
-        </is>
-      </c>
-      <c r="I587" t="inlineStr">
-        <is>
-          <t>carbon black</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>market for lime, hydrated, loose weight</t>
-        </is>
-      </c>
-      <c r="B588">
-        <v>0.04316546762589928</v>
-      </c>
-      <c r="C588" t="inlineStr">
-        <is>
-          <t>RoW</t>
-        </is>
-      </c>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F588" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G588" t="inlineStr">
-        <is>
-          <t>lime, hydrated, loose weight</t>
-        </is>
-      </c>
-      <c r="I588" t="inlineStr">
-        <is>
-          <t>lime, hydrated, loose weight</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>market for magnesium oxide</t>
-        </is>
-      </c>
-      <c r="B589">
-        <v>0.02158273381294964</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>magnesium oxide</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>magnesium oxide</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t xml:space="preserve">fluoroelastomer gasket compound production, fkm, fe5540 type</t>
         </is>
       </c>
       <c r="B590">
@@ -12042,55 +11905,265 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t xml:space="preserve">fluoroelastomer gasket compound, FKM, FE5540 type</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t xml:space="preserve">fluoroelastomer gasket compound, FKM, FE5540 type</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
+          <t xml:space="preserve">fluoroelastomer production, fkm terpolymer, 75/16/9 molar composition</t>
+        </is>
+      </c>
+      <c r="B591">
+        <v>0.7122302158273381</v>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fluoroelastomer, FKM terpolymer, 75/16/9 molar composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>market for chemical, organic</t>
+        </is>
+      </c>
+      <c r="B592">
+        <v>0.007194244604316547</v>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>chemical, organic</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>chemical, organic</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B593">
+        <v>0.2158273381294964</v>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>market for lime, hydrated, loose weight</t>
+        </is>
+      </c>
+      <c r="B594">
+        <v>0.04316546762589928</v>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>lime, hydrated, loose weight</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>lime, hydrated, loose weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>market for magnesium oxide</t>
+        </is>
+      </c>
+      <c r="B595">
+        <v>0.02158273381294964</v>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>magnesium oxide</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>magnesium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B596">
+        <v>1</v>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
           <t>market for heat, district or industrial, natural gas</t>
         </is>
       </c>
-      <c r="B591">
+      <c r="B597">
         <v>6</v>
       </c>
-      <c r="C591" t="inlineStr">
+      <c r="C597" t="inlineStr">
         <is>
           <t>RoW</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr">
+      <c r="D597" t="inlineStr">
         <is>
           <t>megajoule</t>
         </is>
       </c>
-      <c r="F591" t="inlineStr">
+      <c r="F597" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G591" t="inlineStr">
+      <c r="G597" t="inlineStr">
         <is>
           <t>heat, district or industrial, natural gas</t>
         </is>
       </c>
-      <c r="I591" t="inlineStr">
+      <c r="I597" t="inlineStr">
         <is>
           <t>heat, district or industrial, natural gas</t>
         </is>
